--- a/docs/xlsx/jobs-2026-10-28.xlsx
+++ b/docs/xlsx/jobs-2026-10-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="794">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,2371 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Agricultural Conservation Engineer (100% remote with travel throughout Eastern PA)</t>
+  </si>
+  <si>
+    <t>PA Association of Conservation Districts (PACD)</t>
+  </si>
+  <si>
+    <t>N/A, PA</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$76,000 - $100,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-agricultural-conservation-engineer-100-remote-with-travel-throughout-eastern-pa-na-pennsylvania/7340986205</t>
+  </si>
+  <si>
+    <t>Assistant Wildlife Ambassador Caretaker</t>
+  </si>
+  <si>
+    <t>Balsam Mountain Trust</t>
+  </si>
+  <si>
+    <t>Sylva, NC</t>
+  </si>
+  <si>
+    <t>$17 - $19.25 per hour</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-wildlife-ambassador-caretaker-sylva-north-carolina/6832562353</t>
+  </si>
+  <si>
+    <t>Avian Predator Biologist</t>
+  </si>
+  <si>
+    <t>Wildlife Innovations</t>
+  </si>
+  <si>
+    <t>Coastal San Luis Obispo County, CA</t>
+  </si>
+  <si>
+    <t>$70,000 - $90,000 per year</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-avian-predator-biologist-coastal-san-luis-obispo-county-california/7532271199</t>
+  </si>
+  <si>
+    <t>Biologist I – Private Lands Section</t>
+  </si>
+  <si>
+    <t>North Dakota Game and Fish</t>
+  </si>
+  <si>
+    <t>Dickinson, ND</t>
+  </si>
+  <si>
+    <t>$4,976 - $5,359 per month</t>
+  </si>
+  <si>
+    <t>general-stewardship-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-biologist-i--private-lands-section-dickinson-north-dakota/2102431091</t>
+  </si>
+  <si>
+    <t>Biologist I – Wildlife Resource Section</t>
+  </si>
+  <si>
+    <t>ND Game and Fish</t>
+  </si>
+  <si>
+    <t>Riverdale, ND</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-biologist-i--wildlife-resource-section-bismarck-north-dakota/4891456953</t>
+  </si>
+  <si>
+    <t>Community Stewardship Fellow VISTA</t>
+  </si>
+  <si>
+    <t>Great Peninsula Conservancy</t>
+  </si>
+  <si>
+    <t>Bremerton, WA</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$1,966 per month</t>
+  </si>
+  <si>
+    <t>environmental-education-general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-community-stewardship-fellow-vista-bremerton-washington/2244949407</t>
+  </si>
+  <si>
+    <t>Conservation Easement Coordinator</t>
+  </si>
+  <si>
+    <t>Northwest Arkansas Land Trust</t>
+  </si>
+  <si>
+    <t>Fayetteville, AR</t>
+  </si>
+  <si>
+    <t>$45,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-easement-coordinator-fayetteville-arkansas/1675352606</t>
+  </si>
+  <si>
+    <t>Conservation Education Fellow VISTA</t>
+  </si>
+  <si>
+    <t>environmental-education-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-education-fellow-vista-bremerton-washington/9547139616</t>
+  </si>
+  <si>
+    <t>Database Specialist</t>
+  </si>
+  <si>
+    <t>The Piedmont Environmental Council</t>
+  </si>
+  <si>
+    <t>Warrenton, VA</t>
+  </si>
+  <si>
+    <t>$31.25 - $43.26 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-database-specialist-warrenton-virginia/2451066632</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>Nevada Land Trust</t>
+  </si>
+  <si>
+    <t>Reno, NV</t>
+  </si>
+  <si>
+    <t>$80,000 - $90,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-development-director-reno-nevada/2128695451</t>
+  </si>
+  <si>
+    <t>Donor Development Officer</t>
+  </si>
+  <si>
+    <t>Eastern Environmental Law Center</t>
+  </si>
+  <si>
+    <t>Newark, NJ</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-donor-development-officer-newark-new-jersey/7507184706</t>
+  </si>
+  <si>
+    <t>Environmental Specialist III</t>
+  </si>
+  <si>
+    <t>Florida Department of Environmental Protection</t>
+  </si>
+  <si>
+    <t>Tallahassee, FL</t>
+  </si>
+  <si>
+    <t>$53,560.08 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-specialist-iii-tallahassee-florida/6756833424</t>
+  </si>
+  <si>
+    <t>Farm Bill Wildlife Biologist II - Wetland Specialist</t>
+  </si>
+  <si>
+    <t>Pheasants Forever, Inc., and Quail Forever</t>
+  </si>
+  <si>
+    <t>Warrensburg, MO</t>
+  </si>
+  <si>
+    <t>$47,000 + benefits</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship-restoration-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-farm-bill-wildlife-biologist-ii---wetland-specialist-warrensburg-missouri/1226249775</t>
+  </si>
+  <si>
+    <t>Field Coordinator</t>
+  </si>
+  <si>
+    <t>Utah Conservation Corps</t>
+  </si>
+  <si>
+    <t>Logan, UT</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$18 - $19 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-coordinator-logan-utah/5306962234</t>
+  </si>
+  <si>
+    <t>Fishery Biologist 1- Field Crew for Sucker Research</t>
+  </si>
+  <si>
+    <t>Pacific States Marine Fisheries Commission</t>
+  </si>
+  <si>
+    <t>Klamath, OR</t>
+  </si>
+  <si>
+    <t>$19.58 - $31.54 per hour</t>
+  </si>
+  <si>
+    <t>fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fishery-biologist-1--field-crew-for-sucker-research-klamath-oregon/3461349456</t>
+  </si>
+  <si>
+    <t>Fishery Biologist 2- Juvenile Sucker Research and Monitoring</t>
+  </si>
+  <si>
+    <t>Klamath Falls, OR</t>
+  </si>
+  <si>
+    <t>$61,722 - $97,087 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fishery-biologist-2--juvenile-sucker-research-and-monitoring-klamath-falls-oregon/9897870552</t>
+  </si>
+  <si>
+    <t>Fishery Biologist 3- Sucker Research and Monitoring</t>
+  </si>
+  <si>
+    <t>$89,508 - $116,362 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fishery-biologist-3--sucker-research-and-monitoring-klamath-falls-oregon/2279717297</t>
+  </si>
+  <si>
+    <t>Fixed-Wing Line Pilot, Aircraft Pilot</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Tumwater, WA</t>
+  </si>
+  <si>
+    <t>$6,229 - $8,374 per month</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fixed-wing-line-pilot-aircraft-pilot-tumwater-washington/5294377618</t>
+  </si>
+  <si>
+    <t>Greenhouse Lead</t>
+  </si>
+  <si>
+    <t>Olympia, WA</t>
+  </si>
+  <si>
+    <t>$3,327 - $4,406 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-greenhouse-lead-olympia-washington/4750519591</t>
+  </si>
+  <si>
+    <t>Gulf Coastal Plains Regional Director</t>
+  </si>
+  <si>
+    <t>Amphibian and Reptile Conservancy</t>
+  </si>
+  <si>
+    <t>Southern, MS</t>
+  </si>
+  <si>
+    <t>$70,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-gulf-coastal-plains-regional-director-southern-mississippi/5071524431</t>
+  </si>
+  <si>
+    <t>Illinois Farm Bill Wildlife Biologist I or II</t>
+  </si>
+  <si>
+    <t>Ridgway, IL</t>
+  </si>
+  <si>
+    <t>$40,500 - $52,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-wildlife-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-illinois-farm-bill-wildlife-biologist-i-or-ii-ridgway-illinois/9001451191</t>
+  </si>
+  <si>
+    <t>Lakes Region Conservation Corps Member- Various Locations</t>
+  </si>
+  <si>
+    <t>Lakes Region Conservation Corps</t>
+  </si>
+  <si>
+    <t>Holderness, NH</t>
+  </si>
+  <si>
+    <t>$20,400 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-lakes-region-conservation-corps-member--various-locations-holderness-new-hampshire/7484478952</t>
+  </si>
+  <si>
+    <t>Land Preservation Grants Assistant</t>
+  </si>
+  <si>
+    <t>American Battlefield Trust</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>$46,000 - $52,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-land-preservation-grants-assistant-washington-dc/3754178424</t>
+  </si>
+  <si>
+    <t>Legislative Intern</t>
+  </si>
+  <si>
+    <t>Conservation Colorado</t>
+  </si>
+  <si>
+    <t>Denver, CO</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$25 per hour</t>
+  </si>
+  <si>
+    <t>policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-legislative-intern-denver-colorado/4517666597</t>
+  </si>
+  <si>
+    <t>Missouri Farm Bill Wildlife Biologist I or II</t>
+  </si>
+  <si>
+    <t>Montgomery City &amp; Mexico, MO</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-missouri-farm-bill-wildlife-biologist-i-or-ii-montgomery-city--mexico-missouri/5892912277</t>
+  </si>
+  <si>
+    <t>Nāpuʻu NRM Predator Control &amp; Forest Bird Associate II</t>
+  </si>
+  <si>
+    <t>Research Corporation of the University of Hawaiʻi</t>
+  </si>
+  <si>
+    <t>Kailua-Kona, HI</t>
+  </si>
+  <si>
+    <t>$4,071 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-npuu-nrm-predator-control--forest-bird-associate-ii-kailua-kona-hawaii/1124486423</t>
+  </si>
+  <si>
+    <t>Ohio Farm Bill Wildlife Biologist I or II</t>
+  </si>
+  <si>
+    <t>Marysville, OH</t>
+  </si>
+  <si>
+    <t>$40,000 - $56,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-restoration-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ohio-farm-bill-wildlife-biologist-i-or-ii-marysville-ohio/8318141551</t>
+  </si>
+  <si>
+    <t>Operations Outreach Support Analyst, Environmental Planner</t>
+  </si>
+  <si>
+    <t>$69,348 - $93,288 per year</t>
+  </si>
+  <si>
+    <t>forestry-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-operations-outreach-support-analyst-environmental-planner-olympia-washington/1321274363</t>
+  </si>
+  <si>
+    <t>Paralegal</t>
+  </si>
+  <si>
+    <t>The Conservation Fund</t>
+  </si>
+  <si>
+    <t>Arlington, VA</t>
+  </si>
+  <si>
+    <t>$75,000 - $95,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-paralegal-arlington-virginia/5768522145</t>
+  </si>
+  <si>
+    <t>Park/Historic Site Superintendent IV (Park Superintendent)</t>
+  </si>
+  <si>
+    <t>Texas Parks and Wildlife</t>
+  </si>
+  <si>
+    <t>Toyahvale, TX</t>
+  </si>
+  <si>
+    <t>$6,954.73 - $7,954.73 per month</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-parkhistoric-site-superintendent-iv-park-superintendent-toyahvale-texas/8813284589</t>
+  </si>
+  <si>
+    <t>Rangeland Management (Numerous Roles &amp; Locations)</t>
+  </si>
+  <si>
+    <t>US Department of Interior (DOI) | Bureau of Land Management (BLM)</t>
+  </si>
+  <si>
+    <t>Numerous Locations, Other</t>
+  </si>
+  <si>
+    <t>Pay varies based on grade level and duty location for which you're selected.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-rangeland-management-numerous-roles--locations-numerous-locations-other/5052955978</t>
+  </si>
+  <si>
+    <t>Recreation Site Maintenance Foreman</t>
+  </si>
+  <si>
+    <t>Idaho Department of Fish and Game</t>
+  </si>
+  <si>
+    <t>Jerome, ID</t>
+  </si>
+  <si>
+    <t>$25.51 - $31.89 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-recreation-site-maintenance-foreman-jerome-idaho/4962367356</t>
+  </si>
+  <si>
+    <t>Regional Wildlife Biologist - Landowner Sportsmen Coordinator</t>
+  </si>
+  <si>
+    <t>$28.94 - $36.17 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-regional-wildlife-biologist---landowner-sportsmen-coordinator-jerome-idaho/3927070553</t>
+  </si>
+  <si>
+    <t>Restoration Forester, Private Lands (VA)</t>
+  </si>
+  <si>
+    <t>American Forests</t>
+  </si>
+  <si>
+    <t>Marion, VA</t>
+  </si>
+  <si>
+    <t>$25.64 - $33.33 per hour</t>
+  </si>
+  <si>
+    <t>forestry-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-restoration-forester-private-lands-va-marion-virginia/3690288797</t>
+  </si>
+  <si>
+    <t>Sandhills Prescribed Burn Association Coordinator</t>
+  </si>
+  <si>
+    <t>Moore County preferred, NC</t>
+  </si>
+  <si>
+    <t>$50,000 (commensurate with knowledge, skills, and experience).</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sandhills-prescribed-burn-association-coordinator-moore-county-preferred-north-carolina/4764879058</t>
+  </si>
+  <si>
+    <t>Seasonal Bareroot Lead, Forest Nursery Lead</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-seasonal-bareroot-lead-forest-nursery-lead-olympia-washington/9137048120</t>
+  </si>
+  <si>
+    <t>Seasonal Field Team - Crewmember</t>
+  </si>
+  <si>
+    <t>Cumberland River Compact</t>
+  </si>
+  <si>
+    <t>Nashville, TN</t>
+  </si>
+  <si>
+    <t>$18 - $20 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-seasonal-field-team---crewmember-nashville-tennessee/5540923863</t>
+  </si>
+  <si>
+    <t>Stewardship Coordinator</t>
+  </si>
+  <si>
+    <t>Sagebrush Steppe Land Trust</t>
+  </si>
+  <si>
+    <t>Pocatello, ID</t>
+  </si>
+  <si>
+    <t>$55,000 - $65,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-stewardship-coordinator-pocatello-idaho/4457726544</t>
+  </si>
+  <si>
+    <t>Streambank Restoration Technician</t>
+  </si>
+  <si>
+    <t>Stone &amp; Spade, LLC</t>
+  </si>
+  <si>
+    <t>Mills River, NC</t>
+  </si>
+  <si>
+    <t>$22 - $25 per hour</t>
+  </si>
+  <si>
+    <t>restoration-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-streambank-restoration-technician-mills-river-north-carolina/3729458048</t>
+  </si>
+  <si>
+    <t>TerraCorps Community Engagement Coordinator at Providence Neighborhood Planting Program</t>
+  </si>
+  <si>
+    <t>TerraCorps</t>
+  </si>
+  <si>
+    <t>Providence, RI</t>
+  </si>
+  <si>
+    <t>$19,656 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-forestry-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-terracorps-community-engagement-coordinator-at-providence-neighborhood-planting-program-providence-rhode-island/2338458221</t>
+  </si>
+  <si>
+    <t>TerraCorps Land Stewardship Coordinator at Eastie Farm</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-terracorps-land-stewardship-coordinator-at-eastie-farm-boston-massachusetts/6415378028</t>
+  </si>
+  <si>
+    <t>Video Production Specialist</t>
+  </si>
+  <si>
+    <t>Minneapolis-St Paul metro area, MN</t>
+  </si>
+  <si>
+    <t>$60,000 - $65,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-video-production-specialist-minneapolis-st-paul-metro-area-minnesota/4111704193</t>
+  </si>
+  <si>
+    <t>Watershed Restoration &amp; Stewardship Associate</t>
+  </si>
+  <si>
+    <t>River Conservation Corps</t>
+  </si>
+  <si>
+    <t>Rifle, CO</t>
+  </si>
+  <si>
+    <t>$27,000 per year</t>
+  </si>
+  <si>
+    <t>hydrology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-watershed-restoration--stewardship-associate-rifle-colorado/8172031668</t>
+  </si>
+  <si>
+    <t>Watershed Restoration Program Director</t>
+  </si>
+  <si>
+    <t>Borderlands Restoration Network</t>
+  </si>
+  <si>
+    <t>Patagonia, AZ</t>
+  </si>
+  <si>
+    <t>$62,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-hydrology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-watershed-restoration-program-director-patagonia-arizona/4763801336</t>
+  </si>
+  <si>
+    <t>Wildland Fire Regulation and Prevention Technician</t>
+  </si>
+  <si>
+    <t>Deer Park, WA</t>
+  </si>
+  <si>
+    <t>$50,412 - $67,704 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildland-fire-regulation-and-prevention-technician-deer-park-washington/3326338047</t>
+  </si>
+  <si>
+    <t>Corporate Engagement Director</t>
+  </si>
+  <si>
+    <t>Greener By Default</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t>80,000 - 100,000</t>
+  </si>
+  <si>
+    <t>Sustainable Agriculture / Food</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/corporate-engagement-director/</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Lake Waramaug Conservancy</t>
+  </si>
+  <si>
+    <t>Warren, Connecticut, United States</t>
+  </si>
+  <si>
+    <t>100,000 and above</t>
+  </si>
+  <si>
+    <t>Conservation</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/executive-director-213/</t>
+  </si>
+  <si>
+    <t>Senior Attorney for Enforcement Program</t>
+  </si>
+  <si>
+    <t>Felicia Kimble</t>
+  </si>
+  <si>
+    <t>Environmental</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/senior-attorney-for-enforcement-program-3/</t>
+  </si>
+  <si>
+    <t>Administrative Director -Community Programs &amp; Hotlines</t>
+  </si>
+  <si>
+    <t>Safe Horizon</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/635544110fa84facbf75adf7806bb153-administrative-director-community-programs-hotlines-safe-horizon-new-york</t>
+  </si>
+  <si>
+    <t>Assistant Director of Strategic Engagement</t>
+  </si>
+  <si>
+    <t>American Constitution Society</t>
+  </si>
+  <si>
+    <t>Remote (Georgia)</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/10dffb901da94651acf524e34bc4b265-assistant-director-of-strategic-engagement-american-constitution-society-washington</t>
+  </si>
+  <si>
+    <t>Associate Director of Program Implementation</t>
+  </si>
+  <si>
+    <t>Constructive Dialogue Institute</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Conflict Resolution, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7f8675c91bdb4d309a645aaa54117e9a-associate-director-of-program-implementation-constructive-dialogue-institute-new-york</t>
+  </si>
+  <si>
+    <t>Associate, Curriculum Design &amp; Management, What Works Cities (WWC)</t>
+  </si>
+  <si>
+    <t>Results for America</t>
+  </si>
+  <si>
+    <t>USD 72353.00 - 84023.00/year</t>
+  </si>
+  <si>
+    <t>Education, Community Development, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/132da5cffeeb40abbe26860d80685645-associate-curriculum-design-management-what-works-cities-wwc-results-for-america-washington</t>
+  </si>
+  <si>
+    <t>Associate/ Team Member, Non-Profit and Affordable Housing Finance Group</t>
+  </si>
+  <si>
+    <t>Krambo Corporation</t>
+  </si>
+  <si>
+    <t>Ann Arbor, Michigan</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/3f4d7b422ff1424e9aefa12a48147a1d-associate-team-member-non-profit-and-affordable-housing-finance-group-krambo-corporation-ann-arbor</t>
+  </si>
+  <si>
+    <t>Association Operations Manager</t>
+  </si>
+  <si>
+    <t>American Society for Indexing</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 45.00/hour</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8f082cf98e6748bf837a4971ab595775-association-operations-manager-american-society-for-indexing-tempe</t>
+  </si>
+  <si>
+    <t>Attorney: Criminal Appeals &amp; Federal Habeas Corpus Bureau</t>
+  </si>
+  <si>
+    <t>New York State Office of the Attorney General</t>
+  </si>
+  <si>
+    <t>USD 91506.00 - 190644.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/8ac2a9c391344d1ebb9312d90da0ec4d-attorney-criminal-appeals-federal-habeas-corpus-bureau-new-york-state-office-of-the-attorney-general-new-york</t>
+  </si>
+  <si>
+    <t>Bi-Lingual Constituent Services Specialist</t>
+  </si>
+  <si>
+    <t>CUFFH</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/16ae991bac464418aca26a8f28cc3004-bi-lingual-constituent-services-specialist-cuffh-kings-county</t>
+  </si>
+  <si>
+    <t>Clinical Program Coordinator</t>
+  </si>
+  <si>
+    <t>Gateway Arts/Vinfen</t>
+  </si>
+  <si>
+    <t>Brookline, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 42000.00 - 48000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8dcf9c6b701346419d820a6acbd4d29d-clinical-program-coordinator-gateway-artsvinfen-brookline</t>
+  </si>
+  <si>
+    <t>Communications Associate</t>
+  </si>
+  <si>
+    <t>Fractured Atlas</t>
+  </si>
+  <si>
+    <t>USD 32.70 - 32.70/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/20ed199b129f455f92e1a6bc7b8386ce-communications-associate-fractured-atlas-new-york</t>
+  </si>
+  <si>
+    <t>Communications Manager</t>
+  </si>
+  <si>
+    <t>Grantmakers for Effective Organizations</t>
+  </si>
+  <si>
+    <t>USD 77600.00 - 94399.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5c90677b041c4987a439d2d56e34d652-communications-manager-grantmakers-for-effective-organizations-washington</t>
+  </si>
+  <si>
+    <t>Community Democracy Coordinator</t>
+  </si>
+  <si>
+    <t>Fair Shake Environmental Legal Services</t>
+  </si>
+  <si>
+    <t>Remote (Ohio)</t>
+  </si>
+  <si>
+    <t>USD 47000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3a5c059733814ba3aabefac1fd1fb297-community-democracy-coordinator-fair-shake-environmental-legal-services-pittsburgh</t>
+  </si>
+  <si>
+    <t>Community Organizer, Cool the City Campaign</t>
+  </si>
+  <si>
+    <t>Virginia Interfaith Power &amp; Light</t>
+  </si>
+  <si>
+    <t>Richmond, Virginia</t>
+  </si>
+  <si>
+    <t>USD 60000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/64700d9991b748eab134a4e2e2476e43-community-organizer-cool-the-city-campaign-virginia-interfaith-power-light-richmond</t>
+  </si>
+  <si>
+    <t>Contract Paralegal Position</t>
+  </si>
+  <si>
+    <t>UFCW 3000</t>
+  </si>
+  <si>
+    <t>Spokane, Washington</t>
+  </si>
+  <si>
+    <t>USD 26.92 - 40.76/hour</t>
+  </si>
+  <si>
+    <t>Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a3a81d259b4f437ca0d4b7e8f6420435-contract-paralegal-position-ufcw-3000-spokane</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>AIDS Foundation of Chicago</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 102000.00 - 121000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Health Medicine, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/928e80d770c049439319ca949bc58f79-controller-aids-foundation-of-chicago-chicago</t>
+  </si>
+  <si>
+    <t>Deputy Political Director</t>
+  </si>
+  <si>
+    <t>Jewish Voice for Peace</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, International Relations, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a258e66ad6684b279ce7552fe3b253d0-deputy-political-director-jewish-voice-for-peace-washington</t>
+  </si>
+  <si>
+    <t>Development Officer</t>
+  </si>
+  <si>
+    <t>One Mind</t>
+  </si>
+  <si>
+    <t>Rutherford, California</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b88c5a0b88a64a28aa726c760495b563-development-officer-one-mind-rutherford</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>BookSmiles</t>
+  </si>
+  <si>
+    <t>Cherry Hill Township, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/62ab8fff154b4bcdb0eaaff6fa0218ca-director-of-development-booksmiles-cherry-hill-township</t>
+  </si>
+  <si>
+    <t>Director of Development, Individual Philanthropy</t>
+  </si>
+  <si>
+    <t>Food &amp; Friends</t>
+  </si>
+  <si>
+    <t>USD 145000.00 - 155000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ed03c4e7d3e0451d96b05e12a206a3c9-director-of-development-individual-philanthropy-food-friends-washington</t>
+  </si>
+  <si>
+    <t>Director of Finance and Operations</t>
+  </si>
+  <si>
+    <t>College Visions</t>
+  </si>
+  <si>
+    <t>Providence, Rhode Island</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/82dfc32a41964d75bfcd23b9b43ec220-director-of-finance-and-operations-college-visions-providence</t>
+  </si>
+  <si>
+    <t>Director of Financial Assistance</t>
+  </si>
+  <si>
+    <t>Xavier Mission Inc.</t>
+  </si>
+  <si>
+    <t>Remote (New York)</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/79a59b96933c4b3da89c26028c29eb91-director-of-financial-assistance-xavier-mission-inc-new-york</t>
+  </si>
+  <si>
+    <t>Director, Development</t>
+  </si>
+  <si>
+    <t>EveryMind</t>
+  </si>
+  <si>
+    <t>Rockville, Maryland</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/538102368812463e8ee88e5f92d31453-director-development-everymind-rockville</t>
+  </si>
+  <si>
+    <t>Environmental Analyst – Trainer and Technical Assistance Provider (Part-time)</t>
+  </si>
+  <si>
+    <t>NEIWPCC</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 50.00/hour</t>
+  </si>
+  <si>
+    <t>Environment, Science Technology, Water Sanitation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6f03ef40901f458aa54b1bb5cf047725-environmental-analyst-trainer-and-technical-assistance-provider-part-time-neiwpcc-lowell</t>
+  </si>
+  <si>
+    <t>Especialista en Desarrollo de Fondos</t>
+  </si>
+  <si>
+    <t>Fundación Pro Humanae Vitae</t>
+  </si>
+  <si>
+    <t>La Plata, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Community Development, Entrepreneurship, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/37f6fb02287147ac92a5e51204e9d7fb-especialista-en-desarrollo-de-fondos-fundacion-pro-humanae-vitae-la-plata</t>
+  </si>
+  <si>
+    <t>Bronx River Alliance</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/899932cfb20f4497b3120793ae49c6aa-executive-director-bronx-river-alliance-bronx-county</t>
+  </si>
+  <si>
+    <t>Family Engagement Coordinator</t>
+  </si>
+  <si>
+    <t>Hit the Books</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/10c9b8f3254c4dc99e62dc16a3097e6b-family-engagement-coordinator-hit-the-books-new-york</t>
+  </si>
+  <si>
+    <t>Global Health Fellow</t>
+  </si>
+  <si>
+    <t>Center for US Global Leadership</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>International Relations, Economic Development, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cc477e8ef64d47f899956f1ddaf7c733-global-health-fellow-center-for-us-global-leadership-washington</t>
+  </si>
+  <si>
+    <t>Grant Writter para Proyectos Gubernamentales e institucionales</t>
+  </si>
+  <si>
+    <t>Aldeas Infantiles SOS Argentina</t>
+  </si>
+  <si>
+    <t>Buenos Aires, Ciudad Autónoma de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/49ca4d999e60473693969ca8811f4343-grant-writter-para-proyectos-gubernamentales-e-institucionales-aldeas-infantiles-sos-argentina-buenos-aires</t>
+  </si>
+  <si>
+    <t>Grants Officer</t>
+  </si>
+  <si>
+    <t>International Fund for Animal Welfare - IFAW</t>
+  </si>
+  <si>
+    <t>Remote (ZA)</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>ZAR 302900.00 - 360000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Disaster Relief, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/610f2576bebc4590b824664435910d53-grants-officer-international-fund-for-animal-welfare-ifaw-cape-town</t>
+  </si>
+  <si>
+    <t>Head of People &amp; Talent</t>
+  </si>
+  <si>
+    <t>Acumen</t>
+  </si>
+  <si>
+    <t>USD 200000.00 - 225000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/1bfa1017846846358d0172da26055f92-head-of-people-talent-acumen-new-york</t>
+  </si>
+  <si>
+    <t>Head Teacher/TA/Per Diem</t>
+  </si>
+  <si>
+    <t>Union Child Day Care Center DBA Lois Bronz Children's Center</t>
+  </si>
+  <si>
+    <t>White Plains, New York</t>
+  </si>
+  <si>
+    <t>USD 52000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/46aea71cac9449d09a6085ae293d649a-head-teachertaper-diem-union-child-day-care-center-dba-lois-bronz-childrens-center-white-plains</t>
+  </si>
+  <si>
+    <t>Justice in Public Safety Project Counsel</t>
+  </si>
+  <si>
+    <t>NAACP Legal Defense and Educational Fund, Inc.</t>
+  </si>
+  <si>
+    <t>USD 126000.00 - 159000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e01163824ce2463cadeb6c43f603d441-justice-in-public-safety-project-counsel-naacp-legal-defense-and-educational-fund-inc-new-york</t>
+  </si>
+  <si>
+    <t>Atlanta, Georgia</t>
+  </si>
+  <si>
+    <t>USD 109500.00 - 138000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9b6e8d0f62c5414a8b7f78a5c2362e93-justice-in-public-safety-project-counsel-naacp-legal-defense-and-educational-fund-inc-atlanta</t>
+  </si>
+  <si>
+    <t>USD 121000.00 - 152000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/70332cf335144037978da04d542fffd6-justice-in-public-safety-project-counsel-naacp-legal-defense-and-educational-fund-inc-washington</t>
+  </si>
+  <si>
+    <t>Lead Backend Engineer</t>
+  </si>
+  <si>
+    <t>Unified for Progress</t>
+  </si>
+  <si>
+    <t>USD 200000.00 - 240000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/f6780baf17474bd495123fe6a4968857-lead-backend-engineer-unified-for-progress-austin</t>
+  </si>
+  <si>
+    <t>Legal Program and Networks Manager</t>
+  </si>
+  <si>
+    <t>Americans United for Separation of Church and State</t>
+  </si>
+  <si>
+    <t>USD 84394.00 - 103530.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Civic Engagement, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5704d6b455dc44a59c771748f1820c2b-legal-program-and-networks-manager-americans-united-for-separation-of-church-and-state-washington</t>
+  </si>
+  <si>
+    <t>Manager of Operations</t>
+  </si>
+  <si>
+    <t>Interfaith Philadelphia</t>
+  </si>
+  <si>
+    <t>Philadelphia, PA</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b732650932ef4d1cb7d7b00a0bc59622-manager-of-operations-interfaith-philadelphia-philadelphia</t>
+  </si>
+  <si>
+    <t>Medical Case Manager</t>
+  </si>
+  <si>
+    <t>Remote (Chicago, Illinois)</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d8eae2f297a74c8f82433c5d3cc24a70-medical-case-manager-aids-foundation-of-chicago-chicago</t>
+  </si>
+  <si>
+    <t>New York Lead Organizer</t>
+  </si>
+  <si>
+    <t>One Fair Wage</t>
+  </si>
+  <si>
+    <t>NYC, New York</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b7df0b8c986848e8829785c1897703e5-new-york-lead-organizer-one-fair-wage-nyc</t>
+  </si>
+  <si>
+    <t>Office Manager</t>
+  </si>
+  <si>
+    <t>HELPING OTHER PEOPLE EVOLVE</t>
+  </si>
+  <si>
+    <t>Cinnaminson, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>Family, Mental Health, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6c4640ad2b4541689a7d820007ca227a-office-manager-helping-other-people-evolve-cinnaminson</t>
+  </si>
+  <si>
+    <t>Operador/a Hogar Convivencial Niños - Posición Temporal</t>
+  </si>
+  <si>
+    <t>Fundacion Santa Rafaela Maria</t>
+  </si>
+  <si>
+    <t>Beccar, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>ARS 1200000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/61ba04f0d7b4475cb6177964f67d7a5d-operadora-hogar-convivencial-ninos-posicion-temporal-fundacion-santa-rafaela-maria-beccar</t>
+  </si>
+  <si>
+    <t>Part Time Program Coordinator, Boston MA</t>
+  </si>
+  <si>
+    <t>Read to a Child</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5d0beaa7e955482eb9b62d7b4987c88d-part-time-program-coordinator-boston-ma-read-to-a-child-boston</t>
+  </si>
+  <si>
+    <t>Part-time Bryan Innovation Lab Assistant</t>
+  </si>
+  <si>
+    <t>The Steward School</t>
+  </si>
+  <si>
+    <t>Henrico, Virginia</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/433d94e8ac304f9282d5cd04f8357aaf-part-time-bryan-innovation-lab-assistant-the-steward-school-henrico</t>
+  </si>
+  <si>
+    <t>Policy Analyst / Senior Policy Analyst, State Capacity</t>
+  </si>
+  <si>
+    <t>Niskanen Center</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5a86d7f9daed499ebc68a5b56c7445cc-policy-analyst-senior-policy-analyst-state-capacity-niskanen-center-washington</t>
+  </si>
+  <si>
+    <t>Profesional para proyecto de Eventos y Voluntariados Corporativos</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/debd345169fb478aa66e196be9893ac8-profesional-para-proyecto-de-eventos-y-voluntariados-corporativos-aldeas-infantiles-sos-argentina-buenos-aires</t>
+  </si>
+  <si>
+    <t>Program Associate</t>
+  </si>
+  <si>
+    <t>NATIONAL COMMUNITY PHARMACISTS ASSOCIATION FOUNDATION INC</t>
+  </si>
+  <si>
+    <t>USD 49000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Disaster Relief, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3e06148cf7554ca0995a1f8646cc8380-program-associate-national-community-pharmacists-association-foundation-inc-alexandria</t>
+  </si>
+  <si>
+    <t>Program Director</t>
+  </si>
+  <si>
+    <t>YEMBA, Inc.</t>
+  </si>
+  <si>
+    <t>Oak Park, Illinois</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c0fc2a3c2741424f87a1d33a594ae41f-program-director-yemba-inc-oak-park</t>
+  </si>
+  <si>
+    <t>Program Instructor</t>
+  </si>
+  <si>
+    <t>Reach Incorporated</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/26b57aabd0d04bd1bfb13bc4dfb39ef9-program-instructor-reach-incorporated-washington</t>
+  </si>
+  <si>
+    <t>Project Director, Pro Truth Initiative</t>
+  </si>
+  <si>
+    <t>USD 177000.00 - 204000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bfd6cdb29cb2485e8ff6816b1359fd6d-project-director-pro-truth-initiative-naacp-legal-defense-and-educational-fund-inc-washington</t>
+  </si>
+  <si>
+    <t>USD 162500.00 - 186500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a20bdf945ae44bd084b656fc176e6ca1-project-director-pro-truth-initiative-naacp-legal-defense-and-educational-fund-inc-atlanta</t>
+  </si>
+  <si>
+    <t>USD 184000.00 - 212000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/65d865fd9f0545a9b020ba30220a46ce-project-director-pro-truth-initiative-naacp-legal-defense-and-educational-fund-inc-new-york</t>
+  </si>
+  <si>
+    <t>Project Manager, 530A Initiatives</t>
+  </si>
+  <si>
+    <t>NYC Kids RISE</t>
+  </si>
+  <si>
+    <t>Long Island City, New York</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/37adbf3bbcab4c609c3e4efaac7c37a2-project-manager-530a-initiatives-nyc-kids-rise-long-island-city</t>
+  </si>
+  <si>
+    <t>Project Support Specialist</t>
+  </si>
+  <si>
+    <t>Impact Charitable</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/19936abec0c34f8bb5dc4d5cae68ebc1-project-support-specialist-impact-charitable-denver</t>
+  </si>
+  <si>
+    <t>Recuperative Care Caseworker - 1st Shift | 7am - 3:30pm</t>
+  </si>
+  <si>
+    <t>Preble Street</t>
+  </si>
+  <si>
+    <t>Portland, Maine</t>
+  </si>
+  <si>
+    <t>USD 23.82 - 23.82/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/17c16424d5de40d88b217392d10ca5a8-recuperative-care-caseworker-1st-shift-7am-330pm-preble-street-portland</t>
+  </si>
+  <si>
+    <t>Recuperative Care Caseworker - 1st Shift | 7am - 5pm</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/80d029c8c2b94deeb66021d7c7659f18-recuperative-care-caseworker-1st-shift-7am-5pm-preble-street-portland</t>
+  </si>
+  <si>
+    <t>Recuperative Care Caseworker - 2nd Shift</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b3b55de43e24d7484a61b6a96a1e0d6-recuperative-care-caseworker-2nd-shift-preble-street-portland</t>
+  </si>
+  <si>
+    <t>Research and Learning Scientist</t>
+  </si>
+  <si>
+    <t>TalkingPoints</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Family, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c11eba2f6c104c13b35519488985fe80-research-and-learning-scientist-talkingpoints-san-francisco</t>
+  </si>
+  <si>
+    <t>San Joaquin County Navigator</t>
+  </si>
+  <si>
+    <t>Without Permission</t>
+  </si>
+  <si>
+    <t>Stockton, California</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 22.50/hour</t>
+  </si>
+  <si>
+    <t>Sexual Abuse Human Trafficking</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/595e0763405f49cb87ef367b5d1d1b15-san-joaquin-county-navigator-without-permission-stockton</t>
+  </si>
+  <si>
+    <t>Environmental Integrity Project</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b215bd8982b14b0c86292e98ea86c896-senior-attorney-for-enforcement-program-environmental-integrity-project-washington</t>
+  </si>
+  <si>
+    <t>Senior Campaign Director, 530A Initiatives</t>
+  </si>
+  <si>
+    <t>USD 123200.00 - 150900.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6a8ca39ad32a44f09181b436627360c4-senior-campaign-director-530a-initiatives-nyc-kids-rise-long-island-city</t>
+  </si>
+  <si>
+    <t>Senior Counsel, Litigation</t>
+  </si>
+  <si>
+    <t>USD 142500.00 - 194500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/db22a80e976241cbb7354d4192ca28f7-senior-counsel-litigation-naacp-legal-defense-and-educational-fund-inc-atlanta</t>
+  </si>
+  <si>
+    <t>USD 164000.00 - 224000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a16ecb6c36ba4b65ace39258e1b17af2-senior-counsel-litigation-naacp-legal-defense-and-educational-fund-inc-new-york</t>
+  </si>
+  <si>
+    <t>USD 157000.00 - 216000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5ac965dfe1194c6c962c31fe684462e5-senior-counsel-litigation-naacp-legal-defense-and-educational-fund-inc-washington</t>
+  </si>
+  <si>
+    <t>Senior Director of Development, Major Gifts</t>
+  </si>
+  <si>
+    <t>Union Theological Seminary</t>
+  </si>
+  <si>
+    <t>USD 145000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9f44160ff7e74e2ab45791d125d30e77-senior-director-of-development-major-gifts-union-theological-seminary-new-york</t>
+  </si>
+  <si>
+    <t>Senior Program Manager, Community Development</t>
+  </si>
+  <si>
+    <t>William Guitar Little Foundation</t>
+  </si>
+  <si>
+    <t>Columbia, Missouri</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Housing Homelessness, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3ea7a771065342689672be12a15a33c6-senior-program-manager-community-development-william-guitar-little-foundation-columbia</t>
+  </si>
+  <si>
+    <t>Social Worker- Brooklyn Case Management</t>
+  </si>
+  <si>
+    <t>Jewish Association Serving the Aging</t>
+  </si>
+  <si>
+    <t>Brooklyn, New York</t>
+  </si>
+  <si>
+    <t>USD 66300.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b306d9dacfab4a828e9254ad4e64e325-social-worker-brooklyn-case-management-jewish-association-serving-the-aging-brooklyn</t>
+  </si>
+  <si>
+    <t>Supervising Attorney at Wake County Legal Support Center</t>
+  </si>
+  <si>
+    <t>NC Equal Access to Justice Commission</t>
+  </si>
+  <si>
+    <t>Raleigh, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/79b202ce1b1a4884959cdd4697a15ecf-supervising-attorney-at-wake-county-legal-support-center-nc-equal-access-to-justice-commission-raleigh</t>
+  </si>
+  <si>
+    <t>Vice President of Business Development</t>
+  </si>
+  <si>
+    <t>KenCrest Services</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 158000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6f76f2c95fa1413cb57977aeb7442de8-vice-president-of-business-development-kencrest-services-philadelphia</t>
+  </si>
+  <si>
+    <t>Blue Bell, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/430baf2caf994a2a881b02032bf60244-vice-president-of-business-development-kencrest-services-blue-bell</t>
+  </si>
+  <si>
+    <t>Volunteer Coordinator</t>
+  </si>
+  <si>
+    <t>DonorsChoose</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 23.08 - 23.08/hour</t>
+  </si>
+  <si>
+    <t>Education, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3a16a8ca6a594bb39cb6c7be9fa3d623-volunteer-coordinator-donorschoose-new-york</t>
+  </si>
+  <si>
+    <t>Volunteer Manger and Executive Assistant</t>
+  </si>
+  <si>
+    <t>FATHER MCKENNA CENTER INC</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bfd79ba350fa4db4afa9cabed366b286-volunteer-manger-and-executive-assistant-father-mckenna-center-inc-washington</t>
+  </si>
+  <si>
+    <t>ACCOUNT EXECUTIVE</t>
+  </si>
+  <si>
+    <t>Four Star Mushrooms</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Sales</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74360823</t>
+  </si>
+  <si>
+    <t>ADMINISTRATIVE ASSISTANT</t>
+  </si>
+  <si>
+    <t>Federation of Southern Cooperatives Land Assistance Fund</t>
+  </si>
+  <si>
+    <t>Columbia, South Caroliina</t>
+  </si>
+  <si>
+    <t>Administrative</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74402371</t>
+  </si>
+  <si>
+    <t>AGRICULTURE EXTENSION ASSOCIATE</t>
+  </si>
+  <si>
+    <t>University of Kentucky</t>
+  </si>
+  <si>
+    <t>Lexington, Kentucky</t>
+  </si>
+  <si>
+    <t>Program Operations</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74390151</t>
+  </si>
+  <si>
+    <t>AGROFORESTER</t>
+  </si>
+  <si>
+    <t>Appalachian Sustainable Development</t>
+  </si>
+  <si>
+    <t>Bristol, Virginia</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74379153</t>
+  </si>
+  <si>
+    <t>ASSISTANT GARDEN MANAGER</t>
+  </si>
+  <si>
+    <t>Gould Farm</t>
+  </si>
+  <si>
+    <t>Monterey, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74332717</t>
+  </si>
+  <si>
+    <t>CERTIFICATION SPECIALIST II</t>
+  </si>
+  <si>
+    <t>HANDLING DEPARTMENT - NOFA NY</t>
+  </si>
+  <si>
+    <t>Remote in New York, New York</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74344937</t>
+  </si>
+  <si>
+    <t>DEPUTY ADMINISTRATOR FOR SPECIALTY CROPS PROGRAM</t>
+  </si>
+  <si>
+    <t>AMS - USDA</t>
+  </si>
+  <si>
+    <t>Washington DC, Washington DC</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74399927</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT ASSOCIATE</t>
+  </si>
+  <si>
+    <t>Tilth Alliance</t>
+  </si>
+  <si>
+    <t>Hybrid in Seattle, Washington</t>
+  </si>
+  <si>
+    <t>Fund Development</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74385263</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT MANAGER</t>
+  </si>
+  <si>
+    <t>Food to Power</t>
+  </si>
+  <si>
+    <t>Colorado Springs, Colorado</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74376709</t>
+  </si>
+  <si>
+    <t>DIGITAL CONTENT SPECIALIST</t>
+  </si>
+  <si>
+    <t>Gleaners Food Bank of Indiana</t>
+  </si>
+  <si>
+    <t>Indianapolis, Indiana</t>
+  </si>
+  <si>
+    <t>Communications &amp; Outreach</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74351047</t>
+  </si>
+  <si>
+    <t>DIRECTOR</t>
+  </si>
+  <si>
+    <t>COMMUNITY FOOD AND NUTRITION SERVICES - San Antonio Food Bank</t>
+  </si>
+  <si>
+    <t>San Antonio, Texas</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74357157</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF PROGRAMS AND COMMUNITY</t>
+  </si>
+  <si>
+    <t>PART TIME - Open Fields Alliance</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74391373</t>
+  </si>
+  <si>
+    <t>EDUCATION AND OUTREACH SPECIALIST OF THE FOOD RECOVERY INITIATIVE</t>
+  </si>
+  <si>
+    <t>Joint Venture Silicon Valley</t>
+  </si>
+  <si>
+    <t>Remote, with some travel to Santa Clara, Californi</t>
+  </si>
+  <si>
+    <t>Project Management</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74349825</t>
+  </si>
+  <si>
+    <t>EDUCATION COORDINATOR</t>
+  </si>
+  <si>
+    <t>AGRICULTURAL RESEARCH AND DEVELOPMENT PROGRAM - Central State University</t>
+  </si>
+  <si>
+    <t>Wilberforce, Ohio</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74338827</t>
+  </si>
+  <si>
+    <t>EDUCATION PROGRAM ASSISTANT</t>
+  </si>
+  <si>
+    <t>Baltmore City Public Schools</t>
+  </si>
+  <si>
+    <t>Catonsville, Maryland</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74352269</t>
+  </si>
+  <si>
+    <t>EXECUTIVE DIRECTOR</t>
+  </si>
+  <si>
+    <t>Farm to Consumer Legal Defense Fund</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74337605</t>
+  </si>
+  <si>
+    <t>EXTENSION AGENT</t>
+  </si>
+  <si>
+    <t>POTTER AND MCKEAN COUNTIES - Penn State</t>
+  </si>
+  <si>
+    <t>Potter &amp; McKean Counties, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74363267</t>
+  </si>
+  <si>
+    <t>TIOGA COUNTY - Penn State</t>
+  </si>
+  <si>
+    <t>Tioga County, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74364489</t>
+  </si>
+  <si>
+    <t>CLEARFIELD COUNTY - Penn State</t>
+  </si>
+  <si>
+    <t>Clearfield County, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74365711</t>
+  </si>
+  <si>
+    <t>COLUMBIA COUNTY - Penn State</t>
+  </si>
+  <si>
+    <t>Columbia County, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74366933</t>
+  </si>
+  <si>
+    <t>DAUPHIN COUNTY - Penn State</t>
+  </si>
+  <si>
+    <t>Dauphin County, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74368155</t>
+  </si>
+  <si>
+    <t>FRANKLIN COUNTY - Penn State</t>
+  </si>
+  <si>
+    <t>Franklin County, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74369377</t>
+  </si>
+  <si>
+    <t>LANCASTER COUNTY - Penn State</t>
+  </si>
+  <si>
+    <t>Lancaster County, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74370599</t>
+  </si>
+  <si>
+    <t>FARM AND CLIMATE PROGRAM MANAGER</t>
+  </si>
+  <si>
+    <t>Center for Land Based Learning</t>
+  </si>
+  <si>
+    <t>Woodland, California</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74358379</t>
+  </si>
+  <si>
+    <t>FARM MANAGER</t>
+  </si>
+  <si>
+    <t>Michigan State University Extension</t>
+  </si>
+  <si>
+    <t>Novi and Oakland, Michigan</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74353491</t>
+  </si>
+  <si>
+    <t>FARM STORE ASSISTANT</t>
+  </si>
+  <si>
+    <t>Liberty Prairie</t>
+  </si>
+  <si>
+    <t>Grays Lake, Illinois</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74371821</t>
+  </si>
+  <si>
+    <t>FARM TO SCHOOL REGIONAL PRODUCER ENGAGEMENT SPECIALIST</t>
+  </si>
+  <si>
+    <t>BAY AREA - California Department of Food and Agriculture</t>
+  </si>
+  <si>
+    <t>Bay Area, California</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74362045</t>
+  </si>
+  <si>
+    <t>FARM TO TABLE CHEF AND BOARDING HOUSE MANAGER</t>
+  </si>
+  <si>
+    <t>Deep Springs College</t>
+  </si>
+  <si>
+    <t>Deep Springs Valley, California</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74333939</t>
+  </si>
+  <si>
+    <t>FARMLAND ACCESS MANAGER</t>
+  </si>
+  <si>
+    <t>The Land Connection</t>
+  </si>
+  <si>
+    <t>Champaign, Illinois</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74381597</t>
+  </si>
+  <si>
+    <t>FIELD MANAGER</t>
+  </si>
+  <si>
+    <t>Island Grown Initiative</t>
+  </si>
+  <si>
+    <t>Martha's Vineyard, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74335161</t>
+  </si>
+  <si>
+    <t>FOOD EDUCATION TRAINING MANAGER</t>
+  </si>
+  <si>
+    <t>FoodCorps</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74374265</t>
+  </si>
+  <si>
+    <t>FOOD IS MEDICINE MANAGER</t>
+  </si>
+  <si>
+    <t>Food Bank of Alaska</t>
+  </si>
+  <si>
+    <t>Anchorage, Alaska</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74355935</t>
+  </si>
+  <si>
+    <t>FOOD PANTRY ASSISTANT MANAGER</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74336383</t>
+  </si>
+  <si>
+    <t>GLOBAL FOOD RESEARCH PROGRAM</t>
+  </si>
+  <si>
+    <t>PROJECT COORDINATOR - University of North Carolina</t>
+  </si>
+  <si>
+    <t>Chapel Hill, North Carolina</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74386485</t>
+  </si>
+  <si>
+    <t>HEAD BAKER</t>
+  </si>
+  <si>
+    <t>Philo Ridge Farm</t>
+  </si>
+  <si>
+    <t>Charlotte, Vermont</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74388929</t>
+  </si>
+  <si>
+    <t>JUST CUT PROGRAM MANAGER</t>
+  </si>
+  <si>
+    <t>Center for an Agricultural Economy</t>
+  </si>
+  <si>
+    <t>Hardwick, Vermont</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74384041</t>
+  </si>
+  <si>
+    <t>MUSHROOM RESEARCH CENTER RESEARCH COORDINATOR</t>
+  </si>
+  <si>
+    <t>Penn State</t>
+  </si>
+  <si>
+    <t>University Park, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74347381</t>
+  </si>
+  <si>
+    <t>NY AND NJ OPERATIONS ASSOCIATE</t>
+  </si>
+  <si>
+    <t>American Farmland Trust</t>
+  </si>
+  <si>
+    <t>Hybrid in Saratoga Springs, New York</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74401149</t>
+  </si>
+  <si>
+    <t>PHILANTHROPY OFFICER</t>
+  </si>
+  <si>
+    <t>Food and Friends</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74359601</t>
+  </si>
+  <si>
+    <t>POLICY ANALYST</t>
+  </si>
+  <si>
+    <t>Farmers for Climate Solutions</t>
+  </si>
+  <si>
+    <t>Remote in Canada, Remote</t>
+  </si>
+  <si>
+    <t>Policy &amp; Advocacy</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74354713</t>
+  </si>
+  <si>
+    <t>POSTDOCTORAL SCHOLAR â€“ SEED PRODUCTION SYSTEMS</t>
+  </si>
+  <si>
+    <t>Oregon State University</t>
+  </si>
+  <si>
+    <t>Corvallis, Oregon</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74373043</t>
+  </si>
+  <si>
+    <t>PRODUCER ENGAGEMENT COORDINATOR</t>
+  </si>
+  <si>
+    <t>VERMONT - National Association of State Departments of Agriculture</t>
+  </si>
+  <si>
+    <t>Remote in Vermont, Vermont</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74382819</t>
+  </si>
+  <si>
+    <t>REGIONAL COORDINATOR</t>
+  </si>
+  <si>
+    <t>National Grazing Lands Coalition</t>
+  </si>
+  <si>
+    <t>Castle Pines, Colorado</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74375487</t>
+  </si>
+  <si>
+    <t>SENIOR COORDINATOR</t>
+  </si>
+  <si>
+    <t>SCRATCH COOK PROGRAMS - Chef Ann Foundation</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74348603</t>
+  </si>
+  <si>
+    <t>SENIOR MANAGER COMMUNITY RELATIONS</t>
+  </si>
+  <si>
+    <t>Spoonfuls</t>
+  </si>
+  <si>
+    <t>Newton Center, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74346159</t>
+  </si>
+  <si>
+    <t>SOCIAL ENTERPRISE MANAGER</t>
+  </si>
+  <si>
+    <t>Food First NL</t>
+  </si>
+  <si>
+    <t>St. Johnâ€™s Metro Region or Corner Brook/ Humber</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74380375</t>
+  </si>
+  <si>
+    <t>TRANSPORTATION AND DISPATCH COORDINATOR</t>
+  </si>
+  <si>
+    <t>Wisconsin Food Hub Cooperative</t>
+  </si>
+  <si>
+    <t>Waupaca, Wisconsin</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74387707</t>
+  </si>
+  <si>
+    <t>VICE PRESIDENT OF POLICY</t>
+  </si>
+  <si>
+    <t>FEDERAL - Food Solutions Action</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74340049</t>
+  </si>
+  <si>
+    <t>WEST END FARMERS MARKET AND MOBILE MARKET DIRECTOR</t>
+  </si>
+  <si>
+    <t>Change Today Change Tomorrow</t>
+  </si>
+  <si>
+    <t>Louisville, Kentucky</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74343715</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +2412,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +2438,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +2781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2820,1090 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" t="s">
+        <v>73</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" t="s">
+        <v>79</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" t="s">
+        <v>92</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F18" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F19" t="s">
+        <v>105</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" t="s">
+        <v>109</v>
+      </c>
+      <c r="F20" t="s">
+        <v>105</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>111</v>
+      </c>
+      <c r="B21" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" t="s">
+        <v>113</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>114</v>
+      </c>
+      <c r="F21" t="s">
+        <v>115</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" t="s">
+        <v>118</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>119</v>
+      </c>
+      <c r="F22" t="s">
+        <v>120</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" t="s">
+        <v>125</v>
+      </c>
+      <c r="F23" t="s">
+        <v>126</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" t="s">
+        <v>130</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>131</v>
+      </c>
+      <c r="F24" t="s">
+        <v>57</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>133</v>
+      </c>
+      <c r="B25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C25" t="s">
+        <v>135</v>
+      </c>
+      <c r="D25" t="s">
+        <v>136</v>
+      </c>
+      <c r="E25" t="s">
+        <v>137</v>
+      </c>
+      <c r="F25" t="s">
+        <v>138</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" t="s">
+        <v>141</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>143</v>
+      </c>
+      <c r="B27" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" t="s">
+        <v>145</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>146</v>
+      </c>
+      <c r="F27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>148</v>
+      </c>
+      <c r="B28" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" t="s">
+        <v>149</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>150</v>
+      </c>
+      <c r="F28" t="s">
+        <v>151</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>153</v>
+      </c>
+      <c r="B29" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" t="s">
+        <v>108</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>154</v>
+      </c>
+      <c r="F29" t="s">
+        <v>155</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>157</v>
+      </c>
+      <c r="B30" t="s">
+        <v>158</v>
+      </c>
+      <c r="C30" t="s">
+        <v>159</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>160</v>
+      </c>
+      <c r="F30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>163</v>
+      </c>
+      <c r="B31" t="s">
+        <v>164</v>
+      </c>
+      <c r="C31" t="s">
+        <v>165</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>166</v>
+      </c>
+      <c r="F31" t="s">
+        <v>167</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>169</v>
+      </c>
+      <c r="B32" t="s">
+        <v>170</v>
+      </c>
+      <c r="C32" t="s">
+        <v>171</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>172</v>
+      </c>
+      <c r="F32" t="s">
+        <v>73</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>174</v>
+      </c>
+      <c r="B33" t="s">
+        <v>175</v>
+      </c>
+      <c r="C33" t="s">
+        <v>176</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>177</v>
+      </c>
+      <c r="F33" t="s">
+        <v>167</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>179</v>
+      </c>
+      <c r="B34" t="s">
+        <v>175</v>
+      </c>
+      <c r="C34" t="s">
+        <v>176</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>180</v>
+      </c>
+      <c r="F34" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>182</v>
+      </c>
+      <c r="B35" t="s">
+        <v>183</v>
+      </c>
+      <c r="C35" t="s">
+        <v>184</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>185</v>
+      </c>
+      <c r="F35" t="s">
+        <v>186</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>188</v>
+      </c>
+      <c r="B36" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" t="s">
+        <v>189</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>190</v>
+      </c>
+      <c r="F36" t="s">
+        <v>191</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>193</v>
+      </c>
+      <c r="B37" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D37" t="s">
+        <v>84</v>
+      </c>
+      <c r="E37" t="s">
+        <v>109</v>
+      </c>
+      <c r="F37" t="s">
+        <v>105</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>195</v>
+      </c>
+      <c r="B38" t="s">
+        <v>196</v>
+      </c>
+      <c r="C38" t="s">
+        <v>197</v>
+      </c>
+      <c r="D38" t="s">
+        <v>84</v>
+      </c>
+      <c r="E38" t="s">
+        <v>198</v>
+      </c>
+      <c r="F38" t="s">
+        <v>186</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>200</v>
+      </c>
+      <c r="B39" t="s">
+        <v>201</v>
+      </c>
+      <c r="C39" t="s">
+        <v>202</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>203</v>
+      </c>
+      <c r="F39" t="s">
+        <v>48</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>205</v>
+      </c>
+      <c r="B40" t="s">
+        <v>206</v>
+      </c>
+      <c r="C40" t="s">
+        <v>207</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>208</v>
+      </c>
+      <c r="F40" t="s">
+        <v>209</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>211</v>
+      </c>
+      <c r="B41" t="s">
+        <v>212</v>
+      </c>
+      <c r="C41" t="s">
+        <v>213</v>
+      </c>
+      <c r="D41" t="s">
+        <v>40</v>
+      </c>
+      <c r="E41" t="s">
+        <v>214</v>
+      </c>
+      <c r="F41" t="s">
+        <v>215</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>217</v>
+      </c>
+      <c r="B42" t="s">
+        <v>212</v>
+      </c>
+      <c r="C42" t="s">
+        <v>218</v>
+      </c>
+      <c r="D42" t="s">
+        <v>40</v>
+      </c>
+      <c r="E42" t="s">
+        <v>214</v>
+      </c>
+      <c r="F42" t="s">
+        <v>219</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>221</v>
+      </c>
+      <c r="B43" t="s">
+        <v>76</v>
+      </c>
+      <c r="C43" t="s">
+        <v>222</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>223</v>
+      </c>
+      <c r="F43" t="s">
+        <v>67</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>225</v>
+      </c>
+      <c r="B44" t="s">
+        <v>226</v>
+      </c>
+      <c r="C44" t="s">
+        <v>227</v>
+      </c>
+      <c r="D44" t="s">
+        <v>84</v>
+      </c>
+      <c r="E44" t="s">
+        <v>228</v>
+      </c>
+      <c r="F44" t="s">
+        <v>229</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>231</v>
+      </c>
+      <c r="B45" t="s">
+        <v>232</v>
+      </c>
+      <c r="C45" t="s">
+        <v>233</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>234</v>
+      </c>
+      <c r="F45" t="s">
+        <v>235</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>237</v>
+      </c>
+      <c r="B46" t="s">
+        <v>102</v>
+      </c>
+      <c r="C46" t="s">
+        <v>238</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>239</v>
+      </c>
+      <c r="F46" t="s">
+        <v>105</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -466,7 +3911,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -505,8 +3950,82 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F2" t="s">
+        <v>246</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E3" t="s">
+        <v>251</v>
+      </c>
+      <c r="F3" t="s">
+        <v>252</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C4" t="s">
+        <v>243</v>
+      </c>
+      <c r="D4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" t="s">
+        <v>256</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +4033,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +4072,1714 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F2" t="s">
+        <v>263</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F3" t="s">
+        <v>269</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B4" t="s">
+        <v>272</v>
+      </c>
+      <c r="C4" t="s">
+        <v>243</v>
+      </c>
+      <c r="D4" t="s">
+        <v>261</v>
+      </c>
+      <c r="E4" t="s">
+        <v>273</v>
+      </c>
+      <c r="F4" t="s">
+        <v>274</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C5" t="s">
+        <v>243</v>
+      </c>
+      <c r="D5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E5" t="s">
+        <v>278</v>
+      </c>
+      <c r="F5" t="s">
+        <v>279</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>281</v>
+      </c>
+      <c r="B6" t="s">
+        <v>282</v>
+      </c>
+      <c r="C6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D6" t="s">
+        <v>261</v>
+      </c>
+      <c r="E6" t="s">
+        <v>284</v>
+      </c>
+      <c r="F6" t="s">
+        <v>285</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>287</v>
+      </c>
+      <c r="B7" t="s">
+        <v>288</v>
+      </c>
+      <c r="C7" t="s">
+        <v>243</v>
+      </c>
+      <c r="D7" t="s">
+        <v>289</v>
+      </c>
+      <c r="E7" t="s">
+        <v>290</v>
+      </c>
+      <c r="F7" t="s">
+        <v>291</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>293</v>
+      </c>
+      <c r="B8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" t="s">
+        <v>260</v>
+      </c>
+      <c r="D8" t="s">
+        <v>261</v>
+      </c>
+      <c r="E8" t="s">
+        <v>295</v>
+      </c>
+      <c r="F8" t="s">
+        <v>291</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>297</v>
+      </c>
+      <c r="B9" t="s">
+        <v>298</v>
+      </c>
+      <c r="C9" t="s">
+        <v>299</v>
+      </c>
+      <c r="D9" t="s">
+        <v>261</v>
+      </c>
+      <c r="E9" t="s">
+        <v>300</v>
+      </c>
+      <c r="F9" t="s">
+        <v>291</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>302</v>
+      </c>
+      <c r="B10" t="s">
+        <v>303</v>
+      </c>
+      <c r="C10" t="s">
+        <v>304</v>
+      </c>
+      <c r="D10" t="s">
+        <v>261</v>
+      </c>
+      <c r="E10" t="s">
+        <v>305</v>
+      </c>
+      <c r="F10" t="s">
+        <v>306</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>308</v>
+      </c>
+      <c r="B11" t="s">
+        <v>309</v>
+      </c>
+      <c r="C11" t="s">
+        <v>243</v>
+      </c>
+      <c r="D11" t="s">
+        <v>261</v>
+      </c>
+      <c r="E11" t="s">
+        <v>310</v>
+      </c>
+      <c r="F11" t="s">
+        <v>311</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>313</v>
+      </c>
+      <c r="B12" t="s">
+        <v>314</v>
+      </c>
+      <c r="C12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" t="s">
+        <v>261</v>
+      </c>
+      <c r="E12" t="s">
+        <v>315</v>
+      </c>
+      <c r="F12" t="s">
+        <v>316</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>318</v>
+      </c>
+      <c r="B13" t="s">
+        <v>319</v>
+      </c>
+      <c r="C13" t="s">
+        <v>320</v>
+      </c>
+      <c r="D13" t="s">
+        <v>261</v>
+      </c>
+      <c r="E13" t="s">
+        <v>321</v>
+      </c>
+      <c r="F13" t="s">
+        <v>322</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>324</v>
+      </c>
+      <c r="B14" t="s">
+        <v>325</v>
+      </c>
+      <c r="C14" t="s">
+        <v>326</v>
+      </c>
+      <c r="D14" t="s">
+        <v>261</v>
+      </c>
+      <c r="E14" t="s">
+        <v>327</v>
+      </c>
+      <c r="F14" t="s">
+        <v>328</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>330</v>
+      </c>
+      <c r="B15" t="s">
+        <v>331</v>
+      </c>
+      <c r="C15" t="s">
+        <v>332</v>
+      </c>
+      <c r="D15" t="s">
+        <v>261</v>
+      </c>
+      <c r="E15" t="s">
+        <v>333</v>
+      </c>
+      <c r="F15" t="s">
+        <v>334</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>336</v>
+      </c>
+      <c r="B16" t="s">
+        <v>337</v>
+      </c>
+      <c r="C16" t="s">
+        <v>338</v>
+      </c>
+      <c r="D16" t="s">
+        <v>261</v>
+      </c>
+      <c r="E16" t="s">
+        <v>339</v>
+      </c>
+      <c r="F16" t="s">
+        <v>340</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>342</v>
+      </c>
+      <c r="B17" t="s">
+        <v>343</v>
+      </c>
+      <c r="C17" t="s">
+        <v>243</v>
+      </c>
+      <c r="D17" t="s">
+        <v>261</v>
+      </c>
+      <c r="E17" t="s">
+        <v>344</v>
+      </c>
+      <c r="F17" t="s">
+        <v>345</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>347</v>
+      </c>
+      <c r="B18" t="s">
+        <v>348</v>
+      </c>
+      <c r="C18" t="s">
+        <v>349</v>
+      </c>
+      <c r="D18" t="s">
+        <v>261</v>
+      </c>
+      <c r="E18" t="s">
+        <v>350</v>
+      </c>
+      <c r="F18" t="s">
+        <v>351</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>353</v>
+      </c>
+      <c r="B19" t="s">
+        <v>354</v>
+      </c>
+      <c r="C19" t="s">
+        <v>355</v>
+      </c>
+      <c r="D19" t="s">
+        <v>261</v>
+      </c>
+      <c r="E19" t="s">
+        <v>356</v>
+      </c>
+      <c r="F19" t="s">
+        <v>357</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>359</v>
+      </c>
+      <c r="B20" t="s">
+        <v>360</v>
+      </c>
+      <c r="C20" t="s">
+        <v>130</v>
+      </c>
+      <c r="D20" t="s">
+        <v>261</v>
+      </c>
+      <c r="E20" t="s">
+        <v>361</v>
+      </c>
+      <c r="F20" t="s">
+        <v>362</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>364</v>
+      </c>
+      <c r="B21" t="s">
+        <v>365</v>
+      </c>
+      <c r="C21" t="s">
+        <v>366</v>
+      </c>
+      <c r="D21" t="s">
+        <v>261</v>
+      </c>
+      <c r="E21" t="s">
+        <v>367</v>
+      </c>
+      <c r="F21" t="s">
+        <v>368</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>370</v>
+      </c>
+      <c r="B22" t="s">
+        <v>371</v>
+      </c>
+      <c r="C22" t="s">
+        <v>372</v>
+      </c>
+      <c r="D22" t="s">
+        <v>261</v>
+      </c>
+      <c r="E22" t="s">
+        <v>373</v>
+      </c>
+      <c r="F22" t="s">
+        <v>374</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>376</v>
+      </c>
+      <c r="B23" t="s">
+        <v>377</v>
+      </c>
+      <c r="C23" t="s">
+        <v>378</v>
+      </c>
+      <c r="D23" t="s">
+        <v>261</v>
+      </c>
+      <c r="E23" t="s">
+        <v>379</v>
+      </c>
+      <c r="F23" t="s">
+        <v>380</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>382</v>
+      </c>
+      <c r="B24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C24" t="s">
+        <v>243</v>
+      </c>
+      <c r="D24" t="s">
+        <v>384</v>
+      </c>
+      <c r="E24" t="s">
+        <v>385</v>
+      </c>
+      <c r="F24" t="s">
+        <v>386</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>388</v>
+      </c>
+      <c r="B25" t="s">
+        <v>389</v>
+      </c>
+      <c r="C25" t="s">
+        <v>390</v>
+      </c>
+      <c r="D25" t="s">
+        <v>289</v>
+      </c>
+      <c r="E25" t="s">
+        <v>291</v>
+      </c>
+      <c r="F25" t="s">
+        <v>391</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>248</v>
+      </c>
+      <c r="B26" t="s">
+        <v>393</v>
+      </c>
+      <c r="C26" t="s">
+        <v>394</v>
+      </c>
+      <c r="D26" t="s">
+        <v>261</v>
+      </c>
+      <c r="E26" t="s">
+        <v>395</v>
+      </c>
+      <c r="F26" t="s">
+        <v>396</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>398</v>
+      </c>
+      <c r="B27" t="s">
+        <v>399</v>
+      </c>
+      <c r="C27" t="s">
+        <v>260</v>
+      </c>
+      <c r="D27" t="s">
+        <v>384</v>
+      </c>
+      <c r="E27" t="s">
+        <v>400</v>
+      </c>
+      <c r="F27" t="s">
+        <v>401</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>403</v>
+      </c>
+      <c r="B28" t="s">
+        <v>404</v>
+      </c>
+      <c r="C28" t="s">
+        <v>405</v>
+      </c>
+      <c r="D28" t="s">
+        <v>261</v>
+      </c>
+      <c r="E28" t="s">
+        <v>406</v>
+      </c>
+      <c r="F28" t="s">
+        <v>407</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>409</v>
+      </c>
+      <c r="B29" t="s">
+        <v>410</v>
+      </c>
+      <c r="C29" t="s">
+        <v>411</v>
+      </c>
+      <c r="D29" t="s">
+        <v>289</v>
+      </c>
+      <c r="E29" t="s">
+        <v>291</v>
+      </c>
+      <c r="F29" t="s">
+        <v>412</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>414</v>
+      </c>
+      <c r="B30" t="s">
+        <v>415</v>
+      </c>
+      <c r="C30" t="s">
+        <v>416</v>
+      </c>
+      <c r="D30" t="s">
+        <v>417</v>
+      </c>
+      <c r="E30" t="s">
+        <v>418</v>
+      </c>
+      <c r="F30" t="s">
+        <v>419</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>421</v>
+      </c>
+      <c r="B31" t="s">
+        <v>422</v>
+      </c>
+      <c r="C31" t="s">
+        <v>372</v>
+      </c>
+      <c r="D31" t="s">
+        <v>261</v>
+      </c>
+      <c r="E31" t="s">
+        <v>423</v>
+      </c>
+      <c r="F31" t="s">
+        <v>424</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>426</v>
+      </c>
+      <c r="B32" t="s">
+        <v>427</v>
+      </c>
+      <c r="C32" t="s">
+        <v>428</v>
+      </c>
+      <c r="D32" t="s">
+        <v>261</v>
+      </c>
+      <c r="E32" t="s">
+        <v>429</v>
+      </c>
+      <c r="F32" t="s">
+        <v>430</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>432</v>
+      </c>
+      <c r="B33" t="s">
+        <v>433</v>
+      </c>
+      <c r="C33" t="s">
+        <v>260</v>
+      </c>
+      <c r="D33" t="s">
+        <v>261</v>
+      </c>
+      <c r="E33" t="s">
+        <v>434</v>
+      </c>
+      <c r="F33" t="s">
+        <v>435</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>432</v>
+      </c>
+      <c r="B34" t="s">
+        <v>433</v>
+      </c>
+      <c r="C34" t="s">
+        <v>437</v>
+      </c>
+      <c r="D34" t="s">
+        <v>261</v>
+      </c>
+      <c r="E34" t="s">
+        <v>438</v>
+      </c>
+      <c r="F34" t="s">
+        <v>435</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>432</v>
+      </c>
+      <c r="B35" t="s">
+        <v>433</v>
+      </c>
+      <c r="C35" t="s">
+        <v>405</v>
+      </c>
+      <c r="D35" t="s">
+        <v>261</v>
+      </c>
+      <c r="E35" t="s">
+        <v>440</v>
+      </c>
+      <c r="F35" t="s">
+        <v>435</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>442</v>
+      </c>
+      <c r="B36" t="s">
+        <v>443</v>
+      </c>
+      <c r="C36" t="s">
+        <v>243</v>
+      </c>
+      <c r="D36" t="s">
+        <v>261</v>
+      </c>
+      <c r="E36" t="s">
+        <v>444</v>
+      </c>
+      <c r="F36" t="s">
+        <v>445</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>447</v>
+      </c>
+      <c r="B37" t="s">
+        <v>448</v>
+      </c>
+      <c r="C37" t="s">
+        <v>130</v>
+      </c>
+      <c r="D37" t="s">
+        <v>261</v>
+      </c>
+      <c r="E37" t="s">
+        <v>449</v>
+      </c>
+      <c r="F37" t="s">
+        <v>450</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>452</v>
+      </c>
+      <c r="B38" t="s">
+        <v>453</v>
+      </c>
+      <c r="C38" t="s">
+        <v>454</v>
+      </c>
+      <c r="D38" t="s">
+        <v>261</v>
+      </c>
+      <c r="E38" t="s">
+        <v>455</v>
+      </c>
+      <c r="F38" t="s">
+        <v>291</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>457</v>
+      </c>
+      <c r="B39" t="s">
+        <v>337</v>
+      </c>
+      <c r="C39" t="s">
+        <v>458</v>
+      </c>
+      <c r="D39" t="s">
+        <v>261</v>
+      </c>
+      <c r="E39" t="s">
+        <v>459</v>
+      </c>
+      <c r="F39" t="s">
+        <v>340</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>461</v>
+      </c>
+      <c r="B40" t="s">
+        <v>462</v>
+      </c>
+      <c r="C40" t="s">
+        <v>463</v>
+      </c>
+      <c r="D40" t="s">
+        <v>261</v>
+      </c>
+      <c r="E40" t="s">
+        <v>464</v>
+      </c>
+      <c r="F40" t="s">
+        <v>465</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>467</v>
+      </c>
+      <c r="B41" t="s">
+        <v>468</v>
+      </c>
+      <c r="C41" t="s">
+        <v>469</v>
+      </c>
+      <c r="D41" t="s">
+        <v>384</v>
+      </c>
+      <c r="E41" t="s">
+        <v>470</v>
+      </c>
+      <c r="F41" t="s">
+        <v>471</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>473</v>
+      </c>
+      <c r="B42" t="s">
+        <v>474</v>
+      </c>
+      <c r="C42" t="s">
+        <v>475</v>
+      </c>
+      <c r="D42" t="s">
+        <v>476</v>
+      </c>
+      <c r="E42" t="s">
+        <v>477</v>
+      </c>
+      <c r="F42" t="s">
+        <v>430</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>479</v>
+      </c>
+      <c r="B43" t="s">
+        <v>480</v>
+      </c>
+      <c r="C43" t="s">
+        <v>481</v>
+      </c>
+      <c r="D43" t="s">
+        <v>384</v>
+      </c>
+      <c r="E43" t="s">
+        <v>482</v>
+      </c>
+      <c r="F43" t="s">
+        <v>483</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>485</v>
+      </c>
+      <c r="B44" t="s">
+        <v>486</v>
+      </c>
+      <c r="C44" t="s">
+        <v>487</v>
+      </c>
+      <c r="D44" t="s">
+        <v>384</v>
+      </c>
+      <c r="E44" t="s">
+        <v>488</v>
+      </c>
+      <c r="F44" t="s">
+        <v>368</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>490</v>
+      </c>
+      <c r="B45" t="s">
+        <v>491</v>
+      </c>
+      <c r="C45" t="s">
+        <v>405</v>
+      </c>
+      <c r="D45" t="s">
+        <v>261</v>
+      </c>
+      <c r="E45" t="s">
+        <v>492</v>
+      </c>
+      <c r="F45" t="s">
+        <v>493</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>495</v>
+      </c>
+      <c r="B46" t="s">
+        <v>410</v>
+      </c>
+      <c r="C46" t="s">
+        <v>411</v>
+      </c>
+      <c r="D46" t="s">
+        <v>289</v>
+      </c>
+      <c r="E46" t="s">
+        <v>291</v>
+      </c>
+      <c r="F46" t="s">
+        <v>412</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>497</v>
+      </c>
+      <c r="B47" t="s">
+        <v>498</v>
+      </c>
+      <c r="C47" t="s">
+        <v>243</v>
+      </c>
+      <c r="D47" t="s">
+        <v>261</v>
+      </c>
+      <c r="E47" t="s">
+        <v>499</v>
+      </c>
+      <c r="F47" t="s">
+        <v>500</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>502</v>
+      </c>
+      <c r="B48" t="s">
+        <v>503</v>
+      </c>
+      <c r="C48" t="s">
+        <v>504</v>
+      </c>
+      <c r="D48" t="s">
+        <v>261</v>
+      </c>
+      <c r="E48" t="s">
+        <v>505</v>
+      </c>
+      <c r="F48" t="s">
+        <v>291</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>507</v>
+      </c>
+      <c r="B49" t="s">
+        <v>508</v>
+      </c>
+      <c r="C49" t="s">
+        <v>405</v>
+      </c>
+      <c r="D49" t="s">
+        <v>384</v>
+      </c>
+      <c r="E49" t="s">
+        <v>509</v>
+      </c>
+      <c r="F49" t="s">
+        <v>510</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>512</v>
+      </c>
+      <c r="B50" t="s">
+        <v>433</v>
+      </c>
+      <c r="C50" t="s">
+        <v>405</v>
+      </c>
+      <c r="D50" t="s">
+        <v>261</v>
+      </c>
+      <c r="E50" t="s">
+        <v>513</v>
+      </c>
+      <c r="F50" t="s">
+        <v>435</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>512</v>
+      </c>
+      <c r="B51" t="s">
+        <v>433</v>
+      </c>
+      <c r="C51" t="s">
+        <v>437</v>
+      </c>
+      <c r="D51" t="s">
+        <v>261</v>
+      </c>
+      <c r="E51" t="s">
+        <v>515</v>
+      </c>
+      <c r="F51" t="s">
+        <v>435</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>512</v>
+      </c>
+      <c r="B52" t="s">
+        <v>433</v>
+      </c>
+      <c r="C52" t="s">
+        <v>260</v>
+      </c>
+      <c r="D52" t="s">
+        <v>261</v>
+      </c>
+      <c r="E52" t="s">
+        <v>517</v>
+      </c>
+      <c r="F52" t="s">
+        <v>435</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>519</v>
+      </c>
+      <c r="B53" t="s">
+        <v>520</v>
+      </c>
+      <c r="C53" t="s">
+        <v>521</v>
+      </c>
+      <c r="D53" t="s">
+        <v>261</v>
+      </c>
+      <c r="E53" t="s">
+        <v>522</v>
+      </c>
+      <c r="F53" t="s">
+        <v>523</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>525</v>
+      </c>
+      <c r="B54" t="s">
+        <v>526</v>
+      </c>
+      <c r="C54" t="s">
+        <v>243</v>
+      </c>
+      <c r="D54" t="s">
+        <v>384</v>
+      </c>
+      <c r="E54" t="s">
+        <v>400</v>
+      </c>
+      <c r="F54" t="s">
+        <v>527</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>529</v>
+      </c>
+      <c r="B55" t="s">
+        <v>530</v>
+      </c>
+      <c r="C55" t="s">
+        <v>531</v>
+      </c>
+      <c r="D55" t="s">
+        <v>261</v>
+      </c>
+      <c r="E55" t="s">
+        <v>532</v>
+      </c>
+      <c r="F55" t="s">
+        <v>533</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>535</v>
+      </c>
+      <c r="B56" t="s">
+        <v>530</v>
+      </c>
+      <c r="C56" t="s">
+        <v>531</v>
+      </c>
+      <c r="D56" t="s">
+        <v>261</v>
+      </c>
+      <c r="E56" t="s">
+        <v>532</v>
+      </c>
+      <c r="F56" t="s">
+        <v>533</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>537</v>
+      </c>
+      <c r="B57" t="s">
+        <v>530</v>
+      </c>
+      <c r="C57" t="s">
+        <v>531</v>
+      </c>
+      <c r="D57" t="s">
+        <v>261</v>
+      </c>
+      <c r="E57" t="s">
+        <v>532</v>
+      </c>
+      <c r="F57" t="s">
+        <v>533</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>539</v>
+      </c>
+      <c r="B58" t="s">
+        <v>540</v>
+      </c>
+      <c r="C58" t="s">
+        <v>243</v>
+      </c>
+      <c r="D58" t="s">
+        <v>261</v>
+      </c>
+      <c r="E58" t="s">
+        <v>541</v>
+      </c>
+      <c r="F58" t="s">
+        <v>542</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>544</v>
+      </c>
+      <c r="B59" t="s">
+        <v>545</v>
+      </c>
+      <c r="C59" t="s">
+        <v>546</v>
+      </c>
+      <c r="D59" t="s">
+        <v>261</v>
+      </c>
+      <c r="E59" t="s">
+        <v>547</v>
+      </c>
+      <c r="F59" t="s">
+        <v>548</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>254</v>
+      </c>
+      <c r="B60" t="s">
+        <v>550</v>
+      </c>
+      <c r="C60" t="s">
+        <v>243</v>
+      </c>
+      <c r="D60" t="s">
+        <v>261</v>
+      </c>
+      <c r="E60" t="s">
+        <v>551</v>
+      </c>
+      <c r="F60" t="s">
+        <v>552</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>554</v>
+      </c>
+      <c r="B61" t="s">
+        <v>520</v>
+      </c>
+      <c r="C61" t="s">
+        <v>521</v>
+      </c>
+      <c r="D61" t="s">
+        <v>261</v>
+      </c>
+      <c r="E61" t="s">
+        <v>555</v>
+      </c>
+      <c r="F61" t="s">
+        <v>523</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>557</v>
+      </c>
+      <c r="B62" t="s">
+        <v>433</v>
+      </c>
+      <c r="C62" t="s">
+        <v>437</v>
+      </c>
+      <c r="D62" t="s">
+        <v>261</v>
+      </c>
+      <c r="E62" t="s">
+        <v>558</v>
+      </c>
+      <c r="F62" t="s">
+        <v>435</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>557</v>
+      </c>
+      <c r="B63" t="s">
+        <v>433</v>
+      </c>
+      <c r="C63" t="s">
+        <v>260</v>
+      </c>
+      <c r="D63" t="s">
+        <v>261</v>
+      </c>
+      <c r="E63" t="s">
+        <v>560</v>
+      </c>
+      <c r="F63" t="s">
+        <v>435</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>557</v>
+      </c>
+      <c r="B64" t="s">
+        <v>433</v>
+      </c>
+      <c r="C64" t="s">
+        <v>405</v>
+      </c>
+      <c r="D64" t="s">
+        <v>261</v>
+      </c>
+      <c r="E64" t="s">
+        <v>562</v>
+      </c>
+      <c r="F64" t="s">
+        <v>435</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>564</v>
+      </c>
+      <c r="B65" t="s">
+        <v>565</v>
+      </c>
+      <c r="C65" t="s">
+        <v>260</v>
+      </c>
+      <c r="D65" t="s">
+        <v>261</v>
+      </c>
+      <c r="E65" t="s">
+        <v>566</v>
+      </c>
+      <c r="F65" t="s">
+        <v>567</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>569</v>
+      </c>
+      <c r="B66" t="s">
+        <v>570</v>
+      </c>
+      <c r="C66" t="s">
+        <v>571</v>
+      </c>
+      <c r="D66" t="s">
+        <v>261</v>
+      </c>
+      <c r="E66" t="s">
+        <v>572</v>
+      </c>
+      <c r="F66" t="s">
+        <v>573</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>575</v>
+      </c>
+      <c r="B67" t="s">
+        <v>576</v>
+      </c>
+      <c r="C67" t="s">
+        <v>577</v>
+      </c>
+      <c r="D67" t="s">
+        <v>261</v>
+      </c>
+      <c r="E67" t="s">
+        <v>578</v>
+      </c>
+      <c r="F67" t="s">
+        <v>291</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>580</v>
+      </c>
+      <c r="B68" t="s">
+        <v>581</v>
+      </c>
+      <c r="C68" t="s">
+        <v>582</v>
+      </c>
+      <c r="D68" t="s">
+        <v>261</v>
+      </c>
+      <c r="E68" t="s">
+        <v>583</v>
+      </c>
+      <c r="F68" t="s">
+        <v>584</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>586</v>
+      </c>
+      <c r="B69" t="s">
+        <v>587</v>
+      </c>
+      <c r="C69" t="s">
+        <v>588</v>
+      </c>
+      <c r="D69" t="s">
+        <v>261</v>
+      </c>
+      <c r="E69" t="s">
+        <v>589</v>
+      </c>
+      <c r="F69" t="s">
+        <v>590</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>586</v>
+      </c>
+      <c r="B70" t="s">
+        <v>587</v>
+      </c>
+      <c r="C70" t="s">
+        <v>592</v>
+      </c>
+      <c r="D70" t="s">
+        <v>261</v>
+      </c>
+      <c r="E70" t="s">
+        <v>589</v>
+      </c>
+      <c r="F70" t="s">
+        <v>590</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>594</v>
+      </c>
+      <c r="B71" t="s">
+        <v>595</v>
+      </c>
+      <c r="C71" t="s">
+        <v>596</v>
+      </c>
+      <c r="D71" t="s">
+        <v>261</v>
+      </c>
+      <c r="E71" t="s">
+        <v>597</v>
+      </c>
+      <c r="F71" t="s">
+        <v>598</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>600</v>
+      </c>
+      <c r="B72" t="s">
+        <v>601</v>
+      </c>
+      <c r="C72" t="s">
+        <v>405</v>
+      </c>
+      <c r="D72" t="s">
+        <v>261</v>
+      </c>
+      <c r="E72" t="s">
+        <v>459</v>
+      </c>
+      <c r="F72" t="s">
+        <v>602</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -562,7 +5787,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -601,8 +5826,1186 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>604</v>
+      </c>
+      <c r="B2" t="s">
+        <v>605</v>
+      </c>
+      <c r="C2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D2" t="s">
+        <v>291</v>
+      </c>
+      <c r="E2" t="s">
+        <v>291</v>
+      </c>
+      <c r="F2" t="s">
+        <v>606</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>608</v>
+      </c>
+      <c r="B3" t="s">
+        <v>609</v>
+      </c>
+      <c r="C3" t="s">
+        <v>610</v>
+      </c>
+      <c r="D3" t="s">
+        <v>291</v>
+      </c>
+      <c r="E3" t="s">
+        <v>291</v>
+      </c>
+      <c r="F3" t="s">
+        <v>611</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>613</v>
+      </c>
+      <c r="B4" t="s">
+        <v>614</v>
+      </c>
+      <c r="C4" t="s">
+        <v>615</v>
+      </c>
+      <c r="D4" t="s">
+        <v>291</v>
+      </c>
+      <c r="E4" t="s">
+        <v>291</v>
+      </c>
+      <c r="F4" t="s">
+        <v>616</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>618</v>
+      </c>
+      <c r="B5" t="s">
+        <v>619</v>
+      </c>
+      <c r="C5" t="s">
+        <v>620</v>
+      </c>
+      <c r="D5" t="s">
+        <v>291</v>
+      </c>
+      <c r="E5" t="s">
+        <v>291</v>
+      </c>
+      <c r="F5" t="s">
+        <v>616</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>622</v>
+      </c>
+      <c r="B6" t="s">
+        <v>623</v>
+      </c>
+      <c r="C6" t="s">
+        <v>624</v>
+      </c>
+      <c r="D6" t="s">
+        <v>291</v>
+      </c>
+      <c r="E6" t="s">
+        <v>291</v>
+      </c>
+      <c r="F6" t="s">
+        <v>616</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>626</v>
+      </c>
+      <c r="B7" t="s">
+        <v>627</v>
+      </c>
+      <c r="C7" t="s">
+        <v>628</v>
+      </c>
+      <c r="D7" t="s">
+        <v>291</v>
+      </c>
+      <c r="E7" t="s">
+        <v>291</v>
+      </c>
+      <c r="F7" t="s">
+        <v>616</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>630</v>
+      </c>
+      <c r="B8" t="s">
+        <v>631</v>
+      </c>
+      <c r="C8" t="s">
+        <v>632</v>
+      </c>
+      <c r="D8" t="s">
+        <v>291</v>
+      </c>
+      <c r="E8" t="s">
+        <v>291</v>
+      </c>
+      <c r="F8" t="s">
+        <v>611</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>634</v>
+      </c>
+      <c r="B9" t="s">
+        <v>635</v>
+      </c>
+      <c r="C9" t="s">
+        <v>636</v>
+      </c>
+      <c r="D9" t="s">
+        <v>291</v>
+      </c>
+      <c r="E9" t="s">
+        <v>291</v>
+      </c>
+      <c r="F9" t="s">
+        <v>637</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>639</v>
+      </c>
+      <c r="B10" t="s">
+        <v>640</v>
+      </c>
+      <c r="C10" t="s">
+        <v>641</v>
+      </c>
+      <c r="D10" t="s">
+        <v>291</v>
+      </c>
+      <c r="E10" t="s">
+        <v>291</v>
+      </c>
+      <c r="F10" t="s">
+        <v>637</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>643</v>
+      </c>
+      <c r="B11" t="s">
+        <v>644</v>
+      </c>
+      <c r="C11" t="s">
+        <v>645</v>
+      </c>
+      <c r="D11" t="s">
+        <v>291</v>
+      </c>
+      <c r="E11" t="s">
+        <v>291</v>
+      </c>
+      <c r="F11" t="s">
+        <v>646</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>648</v>
+      </c>
+      <c r="B12" t="s">
+        <v>649</v>
+      </c>
+      <c r="C12" t="s">
+        <v>650</v>
+      </c>
+      <c r="D12" t="s">
+        <v>291</v>
+      </c>
+      <c r="E12" t="s">
+        <v>291</v>
+      </c>
+      <c r="F12" t="s">
+        <v>616</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>652</v>
+      </c>
+      <c r="B13" t="s">
+        <v>653</v>
+      </c>
+      <c r="C13" t="s">
+        <v>654</v>
+      </c>
+      <c r="D13" t="s">
+        <v>291</v>
+      </c>
+      <c r="E13" t="s">
+        <v>291</v>
+      </c>
+      <c r="F13" t="s">
+        <v>616</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>656</v>
+      </c>
+      <c r="B14" t="s">
+        <v>657</v>
+      </c>
+      <c r="C14" t="s">
+        <v>658</v>
+      </c>
+      <c r="D14" t="s">
+        <v>291</v>
+      </c>
+      <c r="E14" t="s">
+        <v>291</v>
+      </c>
+      <c r="F14" t="s">
+        <v>659</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>661</v>
+      </c>
+      <c r="B15" t="s">
+        <v>662</v>
+      </c>
+      <c r="C15" t="s">
+        <v>663</v>
+      </c>
+      <c r="D15" t="s">
+        <v>291</v>
+      </c>
+      <c r="E15" t="s">
+        <v>291</v>
+      </c>
+      <c r="F15" t="s">
+        <v>567</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>665</v>
+      </c>
+      <c r="B16" t="s">
+        <v>666</v>
+      </c>
+      <c r="C16" t="s">
+        <v>667</v>
+      </c>
+      <c r="D16" t="s">
+        <v>291</v>
+      </c>
+      <c r="E16" t="s">
+        <v>291</v>
+      </c>
+      <c r="F16" t="s">
+        <v>567</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>669</v>
+      </c>
+      <c r="B17" t="s">
+        <v>670</v>
+      </c>
+      <c r="C17" t="s">
+        <v>654</v>
+      </c>
+      <c r="D17" t="s">
+        <v>291</v>
+      </c>
+      <c r="E17" t="s">
+        <v>291</v>
+      </c>
+      <c r="F17" t="s">
+        <v>248</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>672</v>
+      </c>
+      <c r="B18" t="s">
+        <v>673</v>
+      </c>
+      <c r="C18" t="s">
+        <v>674</v>
+      </c>
+      <c r="D18" t="s">
+        <v>291</v>
+      </c>
+      <c r="E18" t="s">
+        <v>291</v>
+      </c>
+      <c r="F18" t="s">
+        <v>616</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>672</v>
+      </c>
+      <c r="B19" t="s">
+        <v>676</v>
+      </c>
+      <c r="C19" t="s">
+        <v>677</v>
+      </c>
+      <c r="D19" t="s">
+        <v>291</v>
+      </c>
+      <c r="E19" t="s">
+        <v>291</v>
+      </c>
+      <c r="F19" t="s">
+        <v>616</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>672</v>
+      </c>
+      <c r="B20" t="s">
+        <v>679</v>
+      </c>
+      <c r="C20" t="s">
+        <v>680</v>
+      </c>
+      <c r="D20" t="s">
+        <v>291</v>
+      </c>
+      <c r="E20" t="s">
+        <v>291</v>
+      </c>
+      <c r="F20" t="s">
+        <v>616</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>672</v>
+      </c>
+      <c r="B21" t="s">
+        <v>682</v>
+      </c>
+      <c r="C21" t="s">
+        <v>683</v>
+      </c>
+      <c r="D21" t="s">
+        <v>291</v>
+      </c>
+      <c r="E21" t="s">
+        <v>291</v>
+      </c>
+      <c r="F21" t="s">
+        <v>616</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>672</v>
+      </c>
+      <c r="B22" t="s">
+        <v>685</v>
+      </c>
+      <c r="C22" t="s">
+        <v>686</v>
+      </c>
+      <c r="D22" t="s">
+        <v>291</v>
+      </c>
+      <c r="E22" t="s">
+        <v>291</v>
+      </c>
+      <c r="F22" t="s">
+        <v>616</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>672</v>
+      </c>
+      <c r="B23" t="s">
+        <v>688</v>
+      </c>
+      <c r="C23" t="s">
+        <v>689</v>
+      </c>
+      <c r="D23" t="s">
+        <v>291</v>
+      </c>
+      <c r="E23" t="s">
+        <v>291</v>
+      </c>
+      <c r="F23" t="s">
+        <v>616</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>672</v>
+      </c>
+      <c r="B24" t="s">
+        <v>691</v>
+      </c>
+      <c r="C24" t="s">
+        <v>692</v>
+      </c>
+      <c r="D24" t="s">
+        <v>291</v>
+      </c>
+      <c r="E24" t="s">
+        <v>291</v>
+      </c>
+      <c r="F24" t="s">
+        <v>616</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>694</v>
+      </c>
+      <c r="B25" t="s">
+        <v>695</v>
+      </c>
+      <c r="C25" t="s">
+        <v>696</v>
+      </c>
+      <c r="D25" t="s">
+        <v>291</v>
+      </c>
+      <c r="E25" t="s">
+        <v>291</v>
+      </c>
+      <c r="F25" t="s">
+        <v>616</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>698</v>
+      </c>
+      <c r="B26" t="s">
+        <v>699</v>
+      </c>
+      <c r="C26" t="s">
+        <v>700</v>
+      </c>
+      <c r="D26" t="s">
+        <v>291</v>
+      </c>
+      <c r="E26" t="s">
+        <v>291</v>
+      </c>
+      <c r="F26" t="s">
+        <v>616</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>702</v>
+      </c>
+      <c r="B27" t="s">
+        <v>703</v>
+      </c>
+      <c r="C27" t="s">
+        <v>704</v>
+      </c>
+      <c r="D27" t="s">
+        <v>291</v>
+      </c>
+      <c r="E27" t="s">
+        <v>291</v>
+      </c>
+      <c r="F27" t="s">
+        <v>616</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>706</v>
+      </c>
+      <c r="B28" t="s">
+        <v>707</v>
+      </c>
+      <c r="C28" t="s">
+        <v>708</v>
+      </c>
+      <c r="D28" t="s">
+        <v>291</v>
+      </c>
+      <c r="E28" t="s">
+        <v>291</v>
+      </c>
+      <c r="F28" t="s">
+        <v>616</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>710</v>
+      </c>
+      <c r="B29" t="s">
+        <v>711</v>
+      </c>
+      <c r="C29" t="s">
+        <v>712</v>
+      </c>
+      <c r="D29" t="s">
+        <v>291</v>
+      </c>
+      <c r="E29" t="s">
+        <v>291</v>
+      </c>
+      <c r="F29" t="s">
+        <v>616</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>714</v>
+      </c>
+      <c r="B30" t="s">
+        <v>715</v>
+      </c>
+      <c r="C30" t="s">
+        <v>716</v>
+      </c>
+      <c r="D30" t="s">
+        <v>291</v>
+      </c>
+      <c r="E30" t="s">
+        <v>291</v>
+      </c>
+      <c r="F30" t="s">
+        <v>616</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>718</v>
+      </c>
+      <c r="B31" t="s">
+        <v>719</v>
+      </c>
+      <c r="C31" t="s">
+        <v>720</v>
+      </c>
+      <c r="D31" t="s">
+        <v>291</v>
+      </c>
+      <c r="E31" t="s">
+        <v>291</v>
+      </c>
+      <c r="F31" t="s">
+        <v>616</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>722</v>
+      </c>
+      <c r="B32" t="s">
+        <v>723</v>
+      </c>
+      <c r="C32" t="s">
+        <v>654</v>
+      </c>
+      <c r="D32" t="s">
+        <v>291</v>
+      </c>
+      <c r="E32" t="s">
+        <v>291</v>
+      </c>
+      <c r="F32" t="s">
+        <v>616</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>725</v>
+      </c>
+      <c r="B33" t="s">
+        <v>726</v>
+      </c>
+      <c r="C33" t="s">
+        <v>727</v>
+      </c>
+      <c r="D33" t="s">
+        <v>291</v>
+      </c>
+      <c r="E33" t="s">
+        <v>291</v>
+      </c>
+      <c r="F33" t="s">
+        <v>659</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>729</v>
+      </c>
+      <c r="B34" t="s">
+        <v>719</v>
+      </c>
+      <c r="C34" t="s">
+        <v>720</v>
+      </c>
+      <c r="D34" t="s">
+        <v>291</v>
+      </c>
+      <c r="E34" t="s">
+        <v>291</v>
+      </c>
+      <c r="F34" t="s">
+        <v>616</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>731</v>
+      </c>
+      <c r="B35" t="s">
+        <v>732</v>
+      </c>
+      <c r="C35" t="s">
+        <v>733</v>
+      </c>
+      <c r="D35" t="s">
+        <v>291</v>
+      </c>
+      <c r="E35" t="s">
+        <v>291</v>
+      </c>
+      <c r="F35" t="s">
+        <v>659</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>735</v>
+      </c>
+      <c r="B36" t="s">
+        <v>736</v>
+      </c>
+      <c r="C36" t="s">
+        <v>737</v>
+      </c>
+      <c r="D36" t="s">
+        <v>291</v>
+      </c>
+      <c r="E36" t="s">
+        <v>291</v>
+      </c>
+      <c r="F36" t="s">
+        <v>616</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>739</v>
+      </c>
+      <c r="B37" t="s">
+        <v>740</v>
+      </c>
+      <c r="C37" t="s">
+        <v>741</v>
+      </c>
+      <c r="D37" t="s">
+        <v>291</v>
+      </c>
+      <c r="E37" t="s">
+        <v>291</v>
+      </c>
+      <c r="F37" t="s">
+        <v>616</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>743</v>
+      </c>
+      <c r="B38" t="s">
+        <v>744</v>
+      </c>
+      <c r="C38" t="s">
+        <v>745</v>
+      </c>
+      <c r="D38" t="s">
+        <v>291</v>
+      </c>
+      <c r="E38" t="s">
+        <v>291</v>
+      </c>
+      <c r="F38" t="s">
+        <v>746</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>748</v>
+      </c>
+      <c r="B39" t="s">
+        <v>749</v>
+      </c>
+      <c r="C39" t="s">
+        <v>750</v>
+      </c>
+      <c r="D39" t="s">
+        <v>291</v>
+      </c>
+      <c r="E39" t="s">
+        <v>291</v>
+      </c>
+      <c r="F39" t="s">
+        <v>611</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>752</v>
+      </c>
+      <c r="B40" t="s">
+        <v>753</v>
+      </c>
+      <c r="C40" t="s">
+        <v>632</v>
+      </c>
+      <c r="D40" t="s">
+        <v>291</v>
+      </c>
+      <c r="E40" t="s">
+        <v>291</v>
+      </c>
+      <c r="F40" t="s">
+        <v>637</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>755</v>
+      </c>
+      <c r="B41" t="s">
+        <v>756</v>
+      </c>
+      <c r="C41" t="s">
+        <v>757</v>
+      </c>
+      <c r="D41" t="s">
+        <v>291</v>
+      </c>
+      <c r="E41" t="s">
+        <v>291</v>
+      </c>
+      <c r="F41" t="s">
+        <v>758</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>760</v>
+      </c>
+      <c r="B42" t="s">
+        <v>761</v>
+      </c>
+      <c r="C42" t="s">
+        <v>762</v>
+      </c>
+      <c r="D42" t="s">
+        <v>291</v>
+      </c>
+      <c r="E42" t="s">
+        <v>291</v>
+      </c>
+      <c r="F42" t="s">
+        <v>746</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>764</v>
+      </c>
+      <c r="B43" t="s">
+        <v>765</v>
+      </c>
+      <c r="C43" t="s">
+        <v>766</v>
+      </c>
+      <c r="D43" t="s">
+        <v>291</v>
+      </c>
+      <c r="E43" t="s">
+        <v>291</v>
+      </c>
+      <c r="F43" t="s">
+        <v>616</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>768</v>
+      </c>
+      <c r="B44" t="s">
+        <v>769</v>
+      </c>
+      <c r="C44" t="s">
+        <v>770</v>
+      </c>
+      <c r="D44" t="s">
+        <v>291</v>
+      </c>
+      <c r="E44" t="s">
+        <v>291</v>
+      </c>
+      <c r="F44" t="s">
+        <v>616</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>772</v>
+      </c>
+      <c r="B45" t="s">
+        <v>773</v>
+      </c>
+      <c r="C45" t="s">
+        <v>654</v>
+      </c>
+      <c r="D45" t="s">
+        <v>291</v>
+      </c>
+      <c r="E45" t="s">
+        <v>291</v>
+      </c>
+      <c r="F45" t="s">
+        <v>616</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>775</v>
+      </c>
+      <c r="B46" t="s">
+        <v>776</v>
+      </c>
+      <c r="C46" t="s">
+        <v>777</v>
+      </c>
+      <c r="D46" t="s">
+        <v>291</v>
+      </c>
+      <c r="E46" t="s">
+        <v>291</v>
+      </c>
+      <c r="F46" t="s">
+        <v>758</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>779</v>
+      </c>
+      <c r="B47" t="s">
+        <v>780</v>
+      </c>
+      <c r="C47" t="s">
+        <v>781</v>
+      </c>
+      <c r="D47" t="s">
+        <v>291</v>
+      </c>
+      <c r="E47" t="s">
+        <v>291</v>
+      </c>
+      <c r="F47" t="s">
+        <v>616</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>783</v>
+      </c>
+      <c r="B48" t="s">
+        <v>784</v>
+      </c>
+      <c r="C48" t="s">
+        <v>785</v>
+      </c>
+      <c r="D48" t="s">
+        <v>291</v>
+      </c>
+      <c r="E48" t="s">
+        <v>291</v>
+      </c>
+      <c r="F48" t="s">
+        <v>616</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>787</v>
+      </c>
+      <c r="B49" t="s">
+        <v>788</v>
+      </c>
+      <c r="C49" t="s">
+        <v>632</v>
+      </c>
+      <c r="D49" t="s">
+        <v>291</v>
+      </c>
+      <c r="E49" t="s">
+        <v>291</v>
+      </c>
+      <c r="F49" t="s">
+        <v>758</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>790</v>
+      </c>
+      <c r="B50" t="s">
+        <v>791</v>
+      </c>
+      <c r="C50" t="s">
+        <v>792</v>
+      </c>
+      <c r="D50" t="s">
+        <v>291</v>
+      </c>
+      <c r="E50" t="s">
+        <v>291</v>
+      </c>
+      <c r="F50" t="s">
+        <v>616</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-10-28.xlsx
+++ b/docs/xlsx/jobs-2026-10-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="971">
   <si>
     <t>Title</t>
   </si>
@@ -922,6 +922,84 @@
     <t>https://www.idealist.org/en/nonprofit-job/16ae991bac464418aca26a8f28cc3004-bi-lingual-constituent-services-specialist-cuffh-kings-county</t>
   </si>
   <si>
+    <t>Bilingual Counselor Advocate</t>
+  </si>
+  <si>
+    <t>Violence Intervention Program, Inc.</t>
+  </si>
+  <si>
+    <t>USD 30.22 - 30.22/hour</t>
+  </si>
+  <si>
+    <t>Victim Support, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4c6d3c6d84c94e03bd7bc5a4301182f6-bilingual-counselor-advocate-violence-intervention-program-inc-new-york</t>
+  </si>
+  <si>
+    <t>Bilingual Helpline Counselor</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 24.73 - 24.73/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5643bf6b06674d7aac630207dda125df-bilingual-helpline-counselor-violence-intervention-program-inc-new-york</t>
+  </si>
+  <si>
+    <t>Bilingual Housing Specialist</t>
+  </si>
+  <si>
+    <t>USD 31.60 - 31.60/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/58702790a6334cb28ce9ee93f9f8277c-bilingual-housing-specialist-violence-intervention-program-inc-new-york</t>
+  </si>
+  <si>
+    <t>Bilingual Social Worker</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4d383a3282be4c1a8e261f541e9c5a58-bilingual-social-worker-violence-intervention-program-inc-new-york</t>
+  </si>
+  <si>
+    <t>Business Advisor</t>
+  </si>
+  <si>
+    <t>APANO Communities United Fund</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 60657.00 - 67210.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0ba3e8b35b1042ee88bf447c1a5631a0-business-advisor-apano-communities-united-fund-portland</t>
+  </si>
+  <si>
+    <t>Chief Financial and Operating Officer (Part-Time)</t>
+  </si>
+  <si>
+    <t>YW Boston</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/53aa94f53ae64b95982b8db4e53b5d06-chief-financial-and-operating-officer-part-time-yw-boston-boston</t>
+  </si>
+  <si>
     <t>Clinical Program Coordinator</t>
   </si>
   <si>
@@ -988,6 +1066,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/3a5c059733814ba3aabefac1fd1fb297-community-democracy-coordinator-fair-shake-environmental-legal-services-pittsburgh</t>
   </si>
   <si>
+    <t>Community Organizer</t>
+  </si>
+  <si>
+    <t>S.F. Parent Coalition</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 78000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5f912cbcf46d4235b20efc7327252f9b-community-organizer-sf-parent-coalition-san-francisco</t>
+  </si>
+  <si>
     <t>Community Organizer, Cool the City Campaign</t>
   </si>
   <si>
@@ -1042,6 +1138,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/928e80d770c049439319ca949bc58f79-controller-aids-foundation-of-chicago-chicago</t>
   </si>
   <si>
+    <t>Coordinator, Development</t>
+  </si>
+  <si>
+    <t>Marin Agricultural Land Trust</t>
+  </si>
+  <si>
+    <t>Point Reyes Station, California</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 42.00/hour</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/317060d368e1402892cf6ea0b72fbc58-coordinator-development-marin-agricultural-land-trust-point-reyes-station</t>
+  </si>
+  <si>
     <t>Deputy Political Director</t>
   </si>
   <si>
@@ -1144,6 +1258,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/79a59b96933c4b3da89c26028c29eb91-director-of-financial-assistance-xavier-mission-inc-new-york</t>
   </si>
   <si>
+    <t>Director of Grants, Non-Profit and Public Agencies</t>
+  </si>
+  <si>
+    <t>McAllister and Quinn LLC</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 105000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/261de342203c435b95c40791e3cf2008-director-of-grants-non-profit-and-public-agencies-mcallister-and-quinn-llc-washington</t>
+  </si>
+  <si>
     <t>Director, Development</t>
   </si>
   <si>
@@ -1168,9 +1297,6 @@
     <t>NEIWPCC</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 50.00/hour</t>
   </si>
   <si>
@@ -1195,6 +1321,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/37f6fb02287147ac92a5e51204e9d7fb-especialista-en-desarrollo-de-fondos-fundacion-pro-humanae-vitae-la-plata</t>
   </si>
   <si>
+    <t>Executive Assistant &amp; Board Coordinator | 3 month+ temporary assignment | Research Nonprofit</t>
+  </si>
+  <si>
+    <t>TSS - Temporary Staffing + Search</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Science Technology, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/07b622ee5f434a41956ac703544495b0-executive-assistant-board-coordinator-3-month-temporary-assignment-research-nonprofit-tss-temporary-staffing-search-new-york</t>
+  </si>
+  <si>
     <t>Bronx River Alliance</t>
   </si>
   <si>
@@ -1210,6 +1351,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/899932cfb20f4497b3120793ae49c6aa-executive-director-bronx-river-alliance-bronx-county</t>
   </si>
   <si>
+    <t>CASA ROMANTICA CULTURAL CENTER AND GARDENS</t>
+  </si>
+  <si>
+    <t>SAN CLEMENTE, California</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0de27d730b4947ae82aa6bd910119799-executive-director-casa-romantica-cultural-center-and-gardens-san-clemente</t>
+  </si>
+  <si>
+    <t>Hoffman Center for the Arts</t>
+  </si>
+  <si>
+    <t>Manzanita, Oregon</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 76000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/79755b49de264794bc829f44e049f35a-executive-director-hoffman-center-for-the-arts-manzanita</t>
+  </si>
+  <si>
+    <t>Facilities Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Genesis of Ann Arbor</t>
+  </si>
+  <si>
+    <t>Ann Arbor, MI</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6c212a9db8fb4ed89908c4458ab033b1-facilities-operations-coordinator-genesis-of-ann-arbor-ann-arbor</t>
+  </si>
+  <si>
     <t>Family Engagement Coordinator</t>
   </si>
   <si>
@@ -1225,15 +1414,48 @@
     <t>https://www.idealist.org/en/nonprofit-job/10c9b8f3254c4dc99e62dc16a3097e6b-family-engagement-coordinator-hit-the-books-new-york</t>
   </si>
   <si>
+    <t>Finance Associate</t>
+  </si>
+  <si>
+    <t>Geraldine R. Dodge Foundation</t>
+  </si>
+  <si>
+    <t>Newark, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7359cd5e770b489da1af92b828e5a438-finance-associate-geraldine-r-dodge-foundation-newark</t>
+  </si>
+  <si>
+    <t>Fractional Chief of Staff &amp; PM</t>
+  </si>
+  <si>
+    <t>SHARED HARVEST FOUNDATION INC</t>
+  </si>
+  <si>
+    <t>Brea, California</t>
+  </si>
+  <si>
+    <t>USD 3500.00 - 3500.00/month</t>
+  </si>
+  <si>
+    <t>Community Development, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d9939d7ad372408cbf17e67170d913a9-fractional-chief-of-staff-pm-shared-harvest-foundation-inc-brea</t>
+  </si>
+  <si>
     <t>Global Health Fellow</t>
   </si>
   <si>
     <t>Center for US Global Leadership</t>
   </si>
   <si>
-    <t>Washington, District of Columbia</t>
-  </si>
-  <si>
     <t>USD 85000.00 - 110000.00/year</t>
   </si>
   <si>
@@ -1312,6 +1534,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/46aea71cac9449d09a6085ae293d649a-head-teachertaper-diem-union-child-day-care-center-dba-lois-bronz-childrens-center-white-plains</t>
   </si>
   <si>
+    <t>Humanities Washington Director of Marketing &amp; Advancement</t>
+  </si>
+  <si>
+    <t>Clover Search Works</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/7274962b221b42fda50846b598531166-humanities-washington-director-of-marketing-advancement-clover-search-works-seattle</t>
+  </si>
+  <si>
+    <t>Interim Director of Operations &amp; Planning | 4-6 months+ Research Nonprofit</t>
+  </si>
+  <si>
+    <t>USD 52.00 - 58.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/ebcd3075b28f480ab398de703e15f980-interim-director-of-operations-planning-4-6-months-research-nonprofit-tss-temporary-staffing-search-new-york</t>
+  </si>
+  <si>
     <t>Justice in Public Safety Project Counsel</t>
   </si>
   <si>
@@ -1372,6 +1618,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/5704d6b455dc44a59c771748f1820c2b-legal-program-and-networks-manager-americans-united-for-separation-of-church-and-state-washington</t>
   </si>
   <si>
+    <t>Licensed Clinical Social Worker</t>
+  </si>
+  <si>
+    <t>Kings Against Violence Initiative</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Crime Safety, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/21e2d39ead2c43d4a945629c3eb53835-licensed-clinical-social-worker-kings-against-violence-initiative-new-york</t>
+  </si>
+  <si>
+    <t>Major Gifts Officer</t>
+  </si>
+  <si>
+    <t>Jubilee Association of Maryland, Inc.</t>
+  </si>
+  <si>
+    <t>Kensington, MD</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Health Medicine, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dc38fbe29b6a44839fa16891b60645b7-major-gifts-officer-jubilee-association-of-maryland-inc-kensington</t>
+  </si>
+  <si>
     <t>Manager of Operations</t>
   </si>
   <si>
@@ -1387,6 +1666,51 @@
     <t>https://www.idealist.org/en/nonprofit-job/b732650932ef4d1cb7d7b00a0bc59622-manager-of-operations-interfaith-philadelphia-philadelphia</t>
   </si>
   <si>
+    <t>Managing Attorney</t>
+  </si>
+  <si>
+    <t>ACLU of Connecticut</t>
+  </si>
+  <si>
+    <t>Hartford, CT</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/27966da21e434b65831dc2176ada28f8-managing-attorney-aclu-of-connecticut-hartford</t>
+  </si>
+  <si>
+    <t>MAP Engagement Coordinator</t>
+  </si>
+  <si>
+    <t>Brooklyn, NY</t>
+  </si>
+  <si>
+    <t>USD 74000.00 - 76000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/80c1d40783284e03bd55b68e5167402b-map-engagement-coordinator-kings-against-violence-initiative-brooklyn</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Community Specialist (Video and Digital Content Creator)</t>
+  </si>
+  <si>
+    <t>Capital IDEA</t>
+  </si>
+  <si>
+    <t>Austin, Texas</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/54154715dc334d408e5aff0c4d904b38-marketing-community-specialist-video-and-digital-content-creator-capital-idea-austin</t>
+  </si>
+  <si>
     <t>Medical Case Manager</t>
   </si>
   <si>
@@ -1459,9 +1783,6 @@
     <t>Read to a Child</t>
   </si>
   <si>
-    <t>Boston, Massachusetts</t>
-  </si>
-  <si>
     <t>USD 20.00 - 20.00/hour</t>
   </si>
   <si>
@@ -1486,6 +1807,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/433d94e8ac304f9282d5cd04f8357aaf-part-time-bryan-innovation-lab-assistant-the-steward-school-henrico</t>
   </si>
   <si>
+    <t>Peer Leader</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6e62d547177f4cc1bce34ed973b00f86-peer-leader-kings-against-violence-initiative-brooklyn</t>
+  </si>
+  <si>
     <t>Policy Analyst / Senior Policy Analyst, State Capacity</t>
   </si>
   <si>
@@ -1507,6 +1834,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/debd345169fb478aa66e196be9893ac8-profesional-para-proyecto-de-eventos-y-voluntariados-corporativos-aldeas-infantiles-sos-argentina-buenos-aires</t>
   </si>
   <si>
+    <t>Program Assistant, School &amp; Community Programs</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fe22d2b4103d4820a24bb683c1a8e7ae-program-assistant-school-community-programs-kings-against-violence-initiative-brooklyn</t>
+  </si>
+  <si>
     <t>Program Associate</t>
   </si>
   <si>
@@ -1522,6 +1858,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/3e06148cf7554ca0995a1f8646cc8380-program-associate-national-community-pharmacists-association-foundation-inc-alexandria</t>
   </si>
   <si>
+    <t>Program Coordinator (Operations Specialist)</t>
+  </si>
+  <si>
+    <t>Bremerton Foodline</t>
+  </si>
+  <si>
+    <t>Bremerton, Washington</t>
+  </si>
+  <si>
+    <t>USD 23.00/hour</t>
+  </si>
+  <si>
+    <t>Hunger Food Security, Housing Homelessness, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/96621dd49e384354b38a1598fb66933e-program-coordinator-operations-specialist-bremerton-foodline-bremerton</t>
+  </si>
+  <si>
     <t>Program Director</t>
   </si>
   <si>
@@ -1591,6 +1945,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/37adbf3bbcab4c609c3e4efaac7c37a2-project-manager-530a-initiatives-nyc-kids-rise-long-island-city</t>
   </si>
   <si>
+    <t>Project Restore Program Director</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d63b55c8119a4f2a8e58cf70cc75c384-project-restore-program-director-kings-against-violence-initiative-brooklyn</t>
+  </si>
+  <si>
+    <t>Project Restore Program Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c6e2a74a933a42a0ba63b62e7c1e6ebc-project-restore-program-manager-kings-against-violence-initiative-brooklyn</t>
+  </si>
+  <si>
     <t>Project Support Specialist</t>
   </si>
   <si>
@@ -1633,6 +2002,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/0b3b55de43e24d7484a61b6a96a1e0d6-recuperative-care-caseworker-2nd-shift-preble-street-portland</t>
   </si>
   <si>
+    <t>Regional Director of Philanthropy, Western Region</t>
+  </si>
+  <si>
+    <t>Epilepsy Foundation of America</t>
+  </si>
+  <si>
+    <t>Remote (District of Columbia)</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Philanthropy, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1cfd4f3a90074deca82334136f68795e-regional-director-of-philanthropy-western-region-epilepsy-foundation-of-america-washington</t>
+  </si>
+  <si>
     <t>Research and Learning Scientist</t>
   </si>
   <si>
@@ -1723,6 +2110,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/9f44160ff7e74e2ab45791d125d30e77-senior-director-of-development-major-gifts-union-theological-seminary-new-york</t>
   </si>
   <si>
+    <t>Senior Director of Programs</t>
+  </si>
+  <si>
+    <t>Eviction Defense Collaborative</t>
+  </si>
+  <si>
+    <t>USD 165000.00 - 180000.00/year</t>
+  </si>
+  <si>
+    <t>Conflict Resolution, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d8402b8e2fec49dfb9f49d9fcaf388b7-senior-director-of-programs-eviction-defense-collaborative-san-francisco</t>
+  </si>
+  <si>
+    <t>Senior Manager, Accounting &amp; Finance (Michigan Affiliate)</t>
+  </si>
+  <si>
+    <t>Southfield, Michigan</t>
+  </si>
+  <si>
+    <t>USD 37.00 - 39.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c6f9aa6282254a609363e2779788eaa1-senior-manager-accounting-finance-michigan-affiliate-epilepsy-foundation-of-america-southfield</t>
+  </si>
+  <si>
     <t>Senior Program Manager, Community Development</t>
   </si>
   <si>
@@ -1741,6 +2155,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/3ea7a771065342689672be12a15a33c6-senior-program-manager-community-development-william-guitar-little-foundation-columbia</t>
   </si>
   <si>
+    <t>SFILEN Program Manager</t>
+  </si>
+  <si>
+    <t>Asian Americans for Civil Rights and Equality (AACRE)</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/02a08a494b214851b4e841bc07f37b89-sfilen-program-manager-asian-americans-for-civil-rights-and-equality-aacre-san-francisco</t>
+  </si>
+  <si>
     <t>Social Worker- Brooklyn Case Management</t>
   </si>
   <si>
@@ -1756,6 +2185,60 @@
     <t>https://www.idealist.org/en/nonprofit-job/b306d9dacfab4a828e9254ad4e64e325-social-worker-brooklyn-case-management-jewish-association-serving-the-aging-brooklyn</t>
   </si>
   <si>
+    <t>Special Assistant, Shared Services</t>
+  </si>
+  <si>
+    <t>Ocean Conservancy</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1cc73aca9e9346d2a21f618a15c66f5b-special-assistant-shared-services-ocean-conservancy-washington</t>
+  </si>
+  <si>
+    <t>Special Projects Coordinator</t>
+  </si>
+  <si>
+    <t>Protect Borrowers</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Education, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a40fc44266844403b6edb8b4883f2290-special-projects-coordinator-protect-borrowers-washington</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Upper Seven Law</t>
+  </si>
+  <si>
+    <t>Helena, Montana</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cbfde311fc1d4af386edf38a92651165-staff-attorney-upper-seven-law-helena</t>
+  </si>
+  <si>
+    <t>Staff Attorney I (Removal Defense)</t>
+  </si>
+  <si>
+    <t>International Institute of Los Angeles</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 87000.00 - 88000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eec661f5148f4bf4b861f07a2fba425e-staff-attorney-i-removal-defense-international-institute-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
     <t>Supervising Attorney at Wake County Legal Support Center</t>
   </si>
   <si>
@@ -1765,15 +2248,21 @@
     <t>Raleigh, North Carolina</t>
   </si>
   <si>
-    <t>USD 90000.00 - 100000.00/year</t>
-  </si>
-  <si>
     <t>Legal Assistance</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/79b202ce1b1a4884959cdd4697a15ecf-supervising-attorney-at-wake-county-legal-support-center-nc-equal-access-to-justice-commission-raleigh</t>
   </si>
   <si>
+    <t>Technical Program Manager</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/76d5ad78bcf748428d3a179cafe48b18-technical-program-manager-ocean-conservancy-washington</t>
+  </si>
+  <si>
     <t>Vice President of Business Development</t>
   </si>
   <si>
@@ -1796,6 +2285,48 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/430baf2caf994a2a881b02032bf60244-vice-president-of-business-development-kencrest-services-blue-bell</t>
+  </si>
+  <si>
+    <t>Vice President of Programs</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 165000.00 - 185000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d45a77cd6e9840849984ef355014b7b2-vice-president-of-programs-conservation-colorado-denver</t>
+  </si>
+  <si>
+    <t>Violence Interventions Specialist (Hospital-Based)</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 57200.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/12c8f9e850274e6aa6a6e873cdea9826-violence-interventions-specialist-hospital-based-kings-against-violence-initiative-brooklyn</t>
+  </si>
+  <si>
+    <t>Vocational Skills &amp; Job Readiness Training Manager</t>
+  </si>
+  <si>
+    <t>Madison House Autism Foundation, Inc.</t>
+  </si>
+  <si>
+    <t>Dickerson, Maryland</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Job Workplace, Agriculture</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3b3693b7062f4f37a347edb38605815f-vocational-skills-job-readiness-training-manager-madison-house-autism-foundation-inc-dickerson</t>
   </si>
   <si>
     <t>Volunteer Coordinator</t>
@@ -4033,7 +4564,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H111"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -4264,165 +4795,165 @@
         <v>303</v>
       </c>
       <c r="C10" t="s">
+        <v>260</v>
+      </c>
+      <c r="D10" t="s">
+        <v>261</v>
+      </c>
+      <c r="E10" t="s">
         <v>304</v>
       </c>
-      <c r="D10" t="s">
-        <v>261</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>305</v>
       </c>
-      <c r="F10" t="s">
+      <c r="H10" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>307</v>
+      </c>
+      <c r="B11" t="s">
+        <v>303</v>
+      </c>
+      <c r="C11" t="s">
+        <v>260</v>
+      </c>
+      <c r="D11" t="s">
         <v>308</v>
       </c>
-      <c r="B11" t="s">
+      <c r="E11" t="s">
         <v>309</v>
       </c>
-      <c r="C11" t="s">
-        <v>243</v>
-      </c>
-      <c r="D11" t="s">
-        <v>261</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
+        <v>305</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="F11" t="s">
-        <v>311</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>311</v>
+      </c>
+      <c r="B12" t="s">
+        <v>303</v>
+      </c>
+      <c r="C12" t="s">
+        <v>260</v>
+      </c>
+      <c r="D12" t="s">
+        <v>261</v>
+      </c>
+      <c r="E12" t="s">
+        <v>312</v>
+      </c>
+      <c r="F12" t="s">
+        <v>291</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="B12" t="s">
-        <v>314</v>
-      </c>
-      <c r="C12" t="s">
-        <v>130</v>
-      </c>
-      <c r="D12" t="s">
-        <v>261</v>
-      </c>
-      <c r="E12" t="s">
-        <v>315</v>
-      </c>
-      <c r="F12" t="s">
-        <v>316</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B13" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="C13" t="s">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="D13" t="s">
         <v>261</v>
       </c>
       <c r="E13" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F13" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B14" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C14" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="D14" t="s">
         <v>261</v>
       </c>
       <c r="E14" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="F14" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B15" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="C15" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="D15" t="s">
-        <v>261</v>
+        <v>308</v>
       </c>
       <c r="E15" t="s">
-        <v>333</v>
+        <v>291</v>
       </c>
       <c r="F15" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="B16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="C16" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="D16" t="s">
         <v>261</v>
       </c>
       <c r="E16" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="F16" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B17" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="C17" t="s">
         <v>243</v>
@@ -4431,516 +4962,516 @@
         <v>261</v>
       </c>
       <c r="E17" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="F17" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="B18" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="C18" t="s">
-        <v>349</v>
+        <v>130</v>
       </c>
       <c r="D18" t="s">
         <v>261</v>
       </c>
       <c r="E18" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="F18" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B19" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="C19" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="D19" t="s">
         <v>261</v>
       </c>
       <c r="E19" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="F19" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B20" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C20" t="s">
-        <v>130</v>
+        <v>352</v>
       </c>
       <c r="D20" t="s">
         <v>261</v>
       </c>
       <c r="E20" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="F20" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B21" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="C21" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="D21" t="s">
         <v>261</v>
       </c>
       <c r="E21" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="F21" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="B22" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="C22" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="D22" t="s">
         <v>261</v>
       </c>
       <c r="E22" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="F22" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="B23" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="C23" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="D23" t="s">
         <v>261</v>
       </c>
       <c r="E23" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="F23" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B24" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="C24" t="s">
-        <v>243</v>
+        <v>376</v>
       </c>
       <c r="D24" t="s">
-        <v>384</v>
+        <v>261</v>
       </c>
       <c r="E24" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="F24" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="B25" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="C25" t="s">
-        <v>390</v>
+        <v>243</v>
       </c>
       <c r="D25" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="E25" t="s">
-        <v>291</v>
+        <v>382</v>
       </c>
       <c r="F25" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>248</v>
+        <v>385</v>
       </c>
       <c r="B26" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="C26" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="D26" t="s">
         <v>261</v>
       </c>
       <c r="E26" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="F26" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="B27" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="C27" t="s">
-        <v>260</v>
+        <v>393</v>
       </c>
       <c r="D27" t="s">
-        <v>384</v>
+        <v>261</v>
       </c>
       <c r="E27" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="F27" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B28" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C28" t="s">
-        <v>405</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s">
         <v>261</v>
       </c>
       <c r="E28" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="F28" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="B29" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="C29" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="E29" t="s">
-        <v>291</v>
+        <v>405</v>
       </c>
       <c r="F29" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="B30" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="C30" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D30" t="s">
-        <v>417</v>
+        <v>261</v>
       </c>
       <c r="E30" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="F30" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="B31" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="C31" t="s">
-        <v>372</v>
+        <v>416</v>
       </c>
       <c r="D31" t="s">
         <v>261</v>
       </c>
       <c r="E31" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="F31" t="s">
-        <v>424</v>
+        <v>291</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="B32" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C32" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="D32" t="s">
         <v>261</v>
       </c>
       <c r="E32" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="F32" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="B33" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="C33" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="D33" t="s">
-        <v>261</v>
+        <v>308</v>
       </c>
       <c r="E33" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="F33" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>430</v>
+      </c>
+      <c r="B34" t="s">
+        <v>431</v>
+      </c>
+      <c r="C34" t="s">
         <v>432</v>
       </c>
-      <c r="B34" t="s">
+      <c r="D34" t="s">
+        <v>289</v>
+      </c>
+      <c r="E34" t="s">
+        <v>291</v>
+      </c>
+      <c r="F34" t="s">
         <v>433</v>
       </c>
-      <c r="C34" t="s">
-        <v>437</v>
-      </c>
-      <c r="D34" t="s">
-        <v>261</v>
-      </c>
-      <c r="E34" t="s">
-        <v>438</v>
-      </c>
-      <c r="F34" t="s">
-        <v>435</v>
-      </c>
       <c r="H34" s="2" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B35" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C35" t="s">
-        <v>405</v>
+        <v>260</v>
       </c>
       <c r="D35" t="s">
-        <v>261</v>
+        <v>289</v>
       </c>
       <c r="E35" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F35" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>248</v>
+      </c>
+      <c r="B36" t="s">
+        <v>440</v>
+      </c>
+      <c r="C36" t="s">
+        <v>441</v>
+      </c>
+      <c r="D36" t="s">
+        <v>261</v>
+      </c>
+      <c r="E36" t="s">
         <v>442</v>
       </c>
-      <c r="B36" t="s">
+      <c r="F36" t="s">
         <v>443</v>
       </c>
-      <c r="C36" t="s">
-        <v>243</v>
-      </c>
-      <c r="D36" t="s">
-        <v>261</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="H36" s="2" t="s">
         <v>444</v>
-      </c>
-      <c r="F36" t="s">
-        <v>445</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>248</v>
+      </c>
+      <c r="B37" t="s">
+        <v>445</v>
+      </c>
+      <c r="C37" t="s">
+        <v>446</v>
+      </c>
+      <c r="D37" t="s">
+        <v>261</v>
+      </c>
+      <c r="E37" t="s">
         <v>447</v>
       </c>
-      <c r="B37" t="s">
+      <c r="F37" t="s">
         <v>448</v>
       </c>
-      <c r="C37" t="s">
-        <v>130</v>
-      </c>
-      <c r="D37" t="s">
-        <v>261</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="H37" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="F37" t="s">
-        <v>450</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>248</v>
+      </c>
+      <c r="B38" t="s">
+        <v>450</v>
+      </c>
+      <c r="C38" t="s">
+        <v>451</v>
+      </c>
+      <c r="D38" t="s">
+        <v>261</v>
+      </c>
+      <c r="E38" t="s">
         <v>452</v>
       </c>
-      <c r="B38" t="s">
+      <c r="F38" t="s">
         <v>453</v>
       </c>
-      <c r="C38" t="s">
+      <c r="H38" s="2" t="s">
         <v>454</v>
-      </c>
-      <c r="D38" t="s">
-        <v>261</v>
-      </c>
-      <c r="E38" t="s">
-        <v>455</v>
-      </c>
-      <c r="F38" t="s">
-        <v>291</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>455</v>
+      </c>
+      <c r="B39" t="s">
+        <v>456</v>
+      </c>
+      <c r="C39" t="s">
         <v>457</v>
       </c>
-      <c r="B39" t="s">
-        <v>337</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
+        <v>261</v>
+      </c>
+      <c r="E39" t="s">
         <v>458</v>
       </c>
-      <c r="D39" t="s">
-        <v>261</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>459</v>
-      </c>
-      <c r="F39" t="s">
-        <v>340</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>460</v>
@@ -4954,125 +5485,125 @@
         <v>462</v>
       </c>
       <c r="C40" t="s">
+        <v>260</v>
+      </c>
+      <c r="D40" t="s">
+        <v>308</v>
+      </c>
+      <c r="E40" t="s">
         <v>463</v>
       </c>
-      <c r="D40" t="s">
-        <v>261</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>464</v>
       </c>
-      <c r="F40" t="s">
+      <c r="H40" s="2" t="s">
         <v>465</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>466</v>
+      </c>
+      <c r="B41" t="s">
         <v>467</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>468</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
+        <v>261</v>
+      </c>
+      <c r="E41" t="s">
         <v>469</v>
       </c>
-      <c r="D41" t="s">
-        <v>384</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>470</v>
       </c>
-      <c r="F41" t="s">
+      <c r="H41" s="2" t="s">
         <v>471</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>472</v>
+      </c>
+      <c r="B42" t="s">
         <v>473</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>474</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
+        <v>289</v>
+      </c>
+      <c r="E42" t="s">
         <v>475</v>
       </c>
-      <c r="D42" t="s">
+      <c r="F42" t="s">
         <v>476</v>
       </c>
-      <c r="E42" t="s">
+      <c r="H42" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="F42" t="s">
-        <v>430</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>478</v>
+      </c>
+      <c r="B43" t="s">
         <v>479</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
+        <v>416</v>
+      </c>
+      <c r="D43" t="s">
+        <v>261</v>
+      </c>
+      <c r="E43" t="s">
         <v>480</v>
       </c>
-      <c r="C43" t="s">
+      <c r="F43" t="s">
         <v>481</v>
       </c>
-      <c r="D43" t="s">
-        <v>384</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="H43" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="F43" t="s">
-        <v>483</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>483</v>
+      </c>
+      <c r="B44" t="s">
+        <v>484</v>
+      </c>
+      <c r="C44" t="s">
         <v>485</v>
       </c>
-      <c r="B44" t="s">
+      <c r="D44" t="s">
+        <v>289</v>
+      </c>
+      <c r="E44" t="s">
+        <v>291</v>
+      </c>
+      <c r="F44" t="s">
         <v>486</v>
       </c>
-      <c r="C44" t="s">
+      <c r="H44" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="D44" t="s">
-        <v>384</v>
-      </c>
-      <c r="E44" t="s">
-        <v>488</v>
-      </c>
-      <c r="F44" t="s">
-        <v>368</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>488</v>
+      </c>
+      <c r="B45" t="s">
+        <v>489</v>
+      </c>
+      <c r="C45" t="s">
         <v>490</v>
       </c>
-      <c r="B45" t="s">
+      <c r="D45" t="s">
         <v>491</v>
-      </c>
-      <c r="C45" t="s">
-        <v>405</v>
-      </c>
-      <c r="D45" t="s">
-        <v>261</v>
       </c>
       <c r="E45" t="s">
         <v>492</v>
@@ -5089,620 +5620,1517 @@
         <v>495</v>
       </c>
       <c r="B46" t="s">
+        <v>496</v>
+      </c>
+      <c r="C46" t="s">
         <v>410</v>
       </c>
-      <c r="C46" t="s">
-        <v>411</v>
-      </c>
       <c r="D46" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="E46" t="s">
-        <v>291</v>
+        <v>497</v>
       </c>
       <c r="F46" t="s">
-        <v>412</v>
+        <v>498</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B47" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C47" t="s">
-        <v>243</v>
+        <v>502</v>
       </c>
       <c r="D47" t="s">
         <v>261</v>
       </c>
       <c r="E47" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F47" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B48" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C48" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D48" t="s">
         <v>261</v>
       </c>
       <c r="E48" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="F48" t="s">
         <v>291</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B49" t="s">
-        <v>508</v>
+        <v>436</v>
       </c>
       <c r="C49" t="s">
-        <v>405</v>
+        <v>260</v>
       </c>
       <c r="D49" t="s">
-        <v>384</v>
+        <v>289</v>
       </c>
       <c r="E49" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F49" t="s">
-        <v>510</v>
+        <v>438</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B50" t="s">
-        <v>433</v>
+        <v>515</v>
       </c>
       <c r="C50" t="s">
-        <v>405</v>
+        <v>260</v>
       </c>
       <c r="D50" t="s">
         <v>261</v>
       </c>
       <c r="E50" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F50" t="s">
-        <v>435</v>
+        <v>517</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B51" t="s">
-        <v>433</v>
+        <v>515</v>
       </c>
       <c r="C51" t="s">
-        <v>437</v>
+        <v>519</v>
       </c>
       <c r="D51" t="s">
         <v>261</v>
       </c>
       <c r="E51" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="F51" t="s">
-        <v>435</v>
+        <v>517</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B52" t="s">
-        <v>433</v>
+        <v>515</v>
       </c>
       <c r="C52" t="s">
-        <v>260</v>
+        <v>416</v>
       </c>
       <c r="D52" t="s">
         <v>261</v>
       </c>
       <c r="E52" t="s">
+        <v>522</v>
+      </c>
+      <c r="F52" t="s">
         <v>517</v>
       </c>
-      <c r="F52" t="s">
-        <v>435</v>
-      </c>
       <c r="H52" s="2" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="B53" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="C53" t="s">
-        <v>521</v>
+        <v>243</v>
       </c>
       <c r="D53" t="s">
         <v>261</v>
       </c>
       <c r="E53" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="F53" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B54" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C54" t="s">
-        <v>243</v>
+        <v>130</v>
       </c>
       <c r="D54" t="s">
-        <v>384</v>
+        <v>261</v>
       </c>
       <c r="E54" t="s">
-        <v>400</v>
+        <v>531</v>
       </c>
       <c r="F54" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="B55" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C55" t="s">
-        <v>531</v>
+        <v>260</v>
       </c>
       <c r="D55" t="s">
         <v>261</v>
       </c>
       <c r="E55" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="F55" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B56" t="s">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="C56" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
       <c r="D56" t="s">
         <v>261</v>
       </c>
       <c r="E56" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="F56" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="B57" t="s">
-        <v>530</v>
+        <v>546</v>
       </c>
       <c r="C57" t="s">
-        <v>531</v>
+        <v>547</v>
       </c>
       <c r="D57" t="s">
         <v>261</v>
       </c>
       <c r="E57" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="F57" t="s">
-        <v>533</v>
+        <v>291</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="B58" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="C58" t="s">
-        <v>243</v>
+        <v>552</v>
       </c>
       <c r="D58" t="s">
         <v>261</v>
       </c>
       <c r="E58" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="F58" t="s">
-        <v>542</v>
+        <v>269</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="B59" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="C59" t="s">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="D59" t="s">
         <v>261</v>
       </c>
       <c r="E59" t="s">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="F59" t="s">
-        <v>548</v>
+        <v>527</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>254</v>
+        <v>559</v>
       </c>
       <c r="B60" t="s">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="C60" t="s">
-        <v>243</v>
+        <v>561</v>
       </c>
       <c r="D60" t="s">
         <v>261</v>
       </c>
       <c r="E60" t="s">
-        <v>551</v>
+        <v>562</v>
       </c>
       <c r="F60" t="s">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="B61" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="C61" t="s">
-        <v>521</v>
+        <v>566</v>
       </c>
       <c r="D61" t="s">
         <v>261</v>
       </c>
       <c r="E61" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="F61" t="s">
-        <v>523</v>
+        <v>372</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="B62" t="s">
-        <v>433</v>
+        <v>570</v>
       </c>
       <c r="C62" t="s">
-        <v>437</v>
+        <v>571</v>
       </c>
       <c r="D62" t="s">
         <v>261</v>
       </c>
       <c r="E62" t="s">
-        <v>558</v>
+        <v>572</v>
       </c>
       <c r="F62" t="s">
-        <v>435</v>
+        <v>573</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>559</v>
+        <v>574</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>557</v>
+        <v>575</v>
       </c>
       <c r="B63" t="s">
-        <v>433</v>
+        <v>576</v>
       </c>
       <c r="C63" t="s">
-        <v>260</v>
+        <v>577</v>
       </c>
       <c r="D63" t="s">
-        <v>261</v>
+        <v>308</v>
       </c>
       <c r="E63" t="s">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="F63" t="s">
-        <v>435</v>
+        <v>579</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>561</v>
+        <v>580</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>557</v>
+        <v>581</v>
       </c>
       <c r="B64" t="s">
-        <v>433</v>
+        <v>582</v>
       </c>
       <c r="C64" t="s">
-        <v>405</v>
+        <v>583</v>
       </c>
       <c r="D64" t="s">
-        <v>261</v>
+        <v>584</v>
       </c>
       <c r="E64" t="s">
-        <v>562</v>
+        <v>585</v>
       </c>
       <c r="F64" t="s">
-        <v>435</v>
+        <v>504</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>563</v>
+        <v>586</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>564</v>
+        <v>587</v>
       </c>
       <c r="B65" t="s">
-        <v>565</v>
+        <v>588</v>
       </c>
       <c r="C65" t="s">
-        <v>260</v>
+        <v>325</v>
       </c>
       <c r="D65" t="s">
-        <v>261</v>
+        <v>308</v>
       </c>
       <c r="E65" t="s">
-        <v>566</v>
+        <v>589</v>
       </c>
       <c r="F65" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>568</v>
+        <v>591</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>569</v>
+        <v>592</v>
       </c>
       <c r="B66" t="s">
-        <v>570</v>
+        <v>593</v>
       </c>
       <c r="C66" t="s">
-        <v>571</v>
+        <v>594</v>
       </c>
       <c r="D66" t="s">
-        <v>261</v>
+        <v>308</v>
       </c>
       <c r="E66" t="s">
-        <v>572</v>
+        <v>595</v>
       </c>
       <c r="F66" t="s">
-        <v>573</v>
+        <v>406</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>574</v>
+        <v>596</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>575</v>
+        <v>597</v>
       </c>
       <c r="B67" t="s">
-        <v>576</v>
+        <v>535</v>
       </c>
       <c r="C67" t="s">
-        <v>577</v>
+        <v>556</v>
       </c>
       <c r="D67" t="s">
-        <v>261</v>
+        <v>308</v>
       </c>
       <c r="E67" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="F67" t="s">
         <v>291</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>579</v>
+        <v>598</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>580</v>
+        <v>599</v>
       </c>
       <c r="B68" t="s">
-        <v>581</v>
+        <v>600</v>
       </c>
       <c r="C68" t="s">
-        <v>582</v>
+        <v>416</v>
       </c>
       <c r="D68" t="s">
         <v>261</v>
       </c>
       <c r="E68" t="s">
-        <v>583</v>
+        <v>601</v>
       </c>
       <c r="F68" t="s">
-        <v>584</v>
+        <v>602</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>585</v>
+        <v>603</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="B69" t="s">
-        <v>587</v>
+        <v>484</v>
       </c>
       <c r="C69" t="s">
-        <v>588</v>
+        <v>485</v>
       </c>
       <c r="D69" t="s">
-        <v>261</v>
+        <v>289</v>
       </c>
       <c r="E69" t="s">
-        <v>589</v>
+        <v>291</v>
       </c>
       <c r="F69" t="s">
-        <v>590</v>
+        <v>486</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>591</v>
+        <v>605</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>586</v>
+        <v>606</v>
       </c>
       <c r="B70" t="s">
-        <v>587</v>
+        <v>535</v>
       </c>
       <c r="C70" t="s">
-        <v>592</v>
+        <v>556</v>
       </c>
       <c r="D70" t="s">
-        <v>261</v>
+        <v>308</v>
       </c>
       <c r="E70" t="s">
-        <v>589</v>
+        <v>607</v>
       </c>
       <c r="F70" t="s">
-        <v>590</v>
+        <v>291</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>593</v>
+        <v>608</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>594</v>
+        <v>609</v>
       </c>
       <c r="B71" t="s">
-        <v>595</v>
+        <v>610</v>
       </c>
       <c r="C71" t="s">
-        <v>596</v>
+        <v>243</v>
       </c>
       <c r="D71" t="s">
         <v>261</v>
       </c>
       <c r="E71" t="s">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="F71" t="s">
-        <v>598</v>
+        <v>612</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>599</v>
+        <v>613</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="B72" t="s">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="C72" t="s">
-        <v>405</v>
+        <v>616</v>
       </c>
       <c r="D72" t="s">
         <v>261</v>
       </c>
       <c r="E72" t="s">
-        <v>459</v>
+        <v>617</v>
       </c>
       <c r="F72" t="s">
-        <v>602</v>
+        <v>618</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>603</v>
+        <v>619</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>620</v>
+      </c>
+      <c r="B73" t="s">
+        <v>621</v>
+      </c>
+      <c r="C73" t="s">
+        <v>622</v>
+      </c>
+      <c r="D73" t="s">
+        <v>261</v>
+      </c>
+      <c r="E73" t="s">
+        <v>623</v>
+      </c>
+      <c r="F73" t="s">
+        <v>291</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>625</v>
+      </c>
+      <c r="B74" t="s">
+        <v>626</v>
+      </c>
+      <c r="C74" t="s">
+        <v>416</v>
+      </c>
+      <c r="D74" t="s">
+        <v>308</v>
+      </c>
+      <c r="E74" t="s">
+        <v>627</v>
+      </c>
+      <c r="F74" t="s">
+        <v>628</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>630</v>
+      </c>
+      <c r="B75" t="s">
+        <v>515</v>
+      </c>
+      <c r="C75" t="s">
+        <v>416</v>
+      </c>
+      <c r="D75" t="s">
+        <v>261</v>
+      </c>
+      <c r="E75" t="s">
+        <v>631</v>
+      </c>
+      <c r="F75" t="s">
+        <v>517</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>630</v>
+      </c>
+      <c r="B76" t="s">
+        <v>515</v>
+      </c>
+      <c r="C76" t="s">
+        <v>519</v>
+      </c>
+      <c r="D76" t="s">
+        <v>261</v>
+      </c>
+      <c r="E76" t="s">
+        <v>633</v>
+      </c>
+      <c r="F76" t="s">
+        <v>517</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>630</v>
+      </c>
+      <c r="B77" t="s">
+        <v>515</v>
+      </c>
+      <c r="C77" t="s">
+        <v>260</v>
+      </c>
+      <c r="D77" t="s">
+        <v>261</v>
+      </c>
+      <c r="E77" t="s">
+        <v>635</v>
+      </c>
+      <c r="F77" t="s">
+        <v>517</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>637</v>
+      </c>
+      <c r="B78" t="s">
+        <v>638</v>
+      </c>
+      <c r="C78" t="s">
+        <v>639</v>
+      </c>
+      <c r="D78" t="s">
+        <v>261</v>
+      </c>
+      <c r="E78" t="s">
+        <v>640</v>
+      </c>
+      <c r="F78" t="s">
+        <v>641</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>643</v>
+      </c>
+      <c r="B79" t="s">
+        <v>535</v>
+      </c>
+      <c r="C79" t="s">
+        <v>556</v>
+      </c>
+      <c r="D79" t="s">
+        <v>261</v>
+      </c>
+      <c r="E79" t="s">
+        <v>644</v>
+      </c>
+      <c r="F79" t="s">
+        <v>537</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>646</v>
+      </c>
+      <c r="B80" t="s">
+        <v>535</v>
+      </c>
+      <c r="C80" t="s">
+        <v>556</v>
+      </c>
+      <c r="D80" t="s">
+        <v>261</v>
+      </c>
+      <c r="E80" t="s">
+        <v>394</v>
+      </c>
+      <c r="F80" t="s">
+        <v>537</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>648</v>
+      </c>
+      <c r="B81" t="s">
+        <v>649</v>
+      </c>
+      <c r="C81" t="s">
+        <v>243</v>
+      </c>
+      <c r="D81" t="s">
+        <v>308</v>
+      </c>
+      <c r="E81" t="s">
+        <v>463</v>
+      </c>
+      <c r="F81" t="s">
+        <v>650</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>652</v>
+      </c>
+      <c r="B82" t="s">
+        <v>653</v>
+      </c>
+      <c r="C82" t="s">
+        <v>654</v>
+      </c>
+      <c r="D82" t="s">
+        <v>261</v>
+      </c>
+      <c r="E82" t="s">
+        <v>655</v>
+      </c>
+      <c r="F82" t="s">
+        <v>656</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>658</v>
+      </c>
+      <c r="B83" t="s">
+        <v>653</v>
+      </c>
+      <c r="C83" t="s">
+        <v>654</v>
+      </c>
+      <c r="D83" t="s">
+        <v>261</v>
+      </c>
+      <c r="E83" t="s">
+        <v>655</v>
+      </c>
+      <c r="F83" t="s">
+        <v>656</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>660</v>
+      </c>
+      <c r="B84" t="s">
+        <v>653</v>
+      </c>
+      <c r="C84" t="s">
+        <v>654</v>
+      </c>
+      <c r="D84" t="s">
+        <v>261</v>
+      </c>
+      <c r="E84" t="s">
+        <v>655</v>
+      </c>
+      <c r="F84" t="s">
+        <v>656</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>662</v>
+      </c>
+      <c r="B85" t="s">
+        <v>663</v>
+      </c>
+      <c r="C85" t="s">
+        <v>664</v>
+      </c>
+      <c r="D85" t="s">
+        <v>261</v>
+      </c>
+      <c r="E85" t="s">
+        <v>665</v>
+      </c>
+      <c r="F85" t="s">
+        <v>666</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>668</v>
+      </c>
+      <c r="B86" t="s">
+        <v>669</v>
+      </c>
+      <c r="C86" t="s">
+        <v>243</v>
+      </c>
+      <c r="D86" t="s">
+        <v>261</v>
+      </c>
+      <c r="E86" t="s">
+        <v>670</v>
+      </c>
+      <c r="F86" t="s">
+        <v>671</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>673</v>
+      </c>
+      <c r="B87" t="s">
+        <v>674</v>
+      </c>
+      <c r="C87" t="s">
+        <v>675</v>
+      </c>
+      <c r="D87" t="s">
+        <v>261</v>
+      </c>
+      <c r="E87" t="s">
+        <v>676</v>
+      </c>
+      <c r="F87" t="s">
+        <v>677</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>254</v>
+      </c>
+      <c r="B88" t="s">
+        <v>679</v>
+      </c>
+      <c r="C88" t="s">
+        <v>243</v>
+      </c>
+      <c r="D88" t="s">
+        <v>261</v>
+      </c>
+      <c r="E88" t="s">
+        <v>680</v>
+      </c>
+      <c r="F88" t="s">
+        <v>681</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>683</v>
+      </c>
+      <c r="B89" t="s">
+        <v>638</v>
+      </c>
+      <c r="C89" t="s">
+        <v>639</v>
+      </c>
+      <c r="D89" t="s">
+        <v>261</v>
+      </c>
+      <c r="E89" t="s">
+        <v>684</v>
+      </c>
+      <c r="F89" t="s">
+        <v>641</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>686</v>
+      </c>
+      <c r="B90" t="s">
+        <v>515</v>
+      </c>
+      <c r="C90" t="s">
+        <v>519</v>
+      </c>
+      <c r="D90" t="s">
+        <v>261</v>
+      </c>
+      <c r="E90" t="s">
+        <v>687</v>
+      </c>
+      <c r="F90" t="s">
+        <v>517</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>686</v>
+      </c>
+      <c r="B91" t="s">
+        <v>515</v>
+      </c>
+      <c r="C91" t="s">
+        <v>260</v>
+      </c>
+      <c r="D91" t="s">
+        <v>261</v>
+      </c>
+      <c r="E91" t="s">
+        <v>689</v>
+      </c>
+      <c r="F91" t="s">
+        <v>517</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>686</v>
+      </c>
+      <c r="B92" t="s">
+        <v>515</v>
+      </c>
+      <c r="C92" t="s">
+        <v>416</v>
+      </c>
+      <c r="D92" t="s">
+        <v>261</v>
+      </c>
+      <c r="E92" t="s">
+        <v>691</v>
+      </c>
+      <c r="F92" t="s">
+        <v>517</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>693</v>
+      </c>
+      <c r="B93" t="s">
+        <v>694</v>
+      </c>
+      <c r="C93" t="s">
+        <v>260</v>
+      </c>
+      <c r="D93" t="s">
+        <v>261</v>
+      </c>
+      <c r="E93" t="s">
+        <v>695</v>
+      </c>
+      <c r="F93" t="s">
+        <v>696</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>698</v>
+      </c>
+      <c r="B94" t="s">
+        <v>699</v>
+      </c>
+      <c r="C94" t="s">
+        <v>352</v>
+      </c>
+      <c r="D94" t="s">
+        <v>261</v>
+      </c>
+      <c r="E94" t="s">
+        <v>700</v>
+      </c>
+      <c r="F94" t="s">
+        <v>701</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>703</v>
+      </c>
+      <c r="B95" t="s">
+        <v>663</v>
+      </c>
+      <c r="C95" t="s">
+        <v>704</v>
+      </c>
+      <c r="D95" t="s">
+        <v>308</v>
+      </c>
+      <c r="E95" t="s">
+        <v>705</v>
+      </c>
+      <c r="F95" t="s">
+        <v>666</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>707</v>
+      </c>
+      <c r="B96" t="s">
+        <v>708</v>
+      </c>
+      <c r="C96" t="s">
+        <v>709</v>
+      </c>
+      <c r="D96" t="s">
+        <v>261</v>
+      </c>
+      <c r="E96" t="s">
+        <v>710</v>
+      </c>
+      <c r="F96" t="s">
+        <v>711</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>713</v>
+      </c>
+      <c r="B97" t="s">
+        <v>714</v>
+      </c>
+      <c r="C97" t="s">
+        <v>352</v>
+      </c>
+      <c r="D97" t="s">
+        <v>261</v>
+      </c>
+      <c r="E97" t="s">
+        <v>715</v>
+      </c>
+      <c r="F97" t="s">
+        <v>716</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>718</v>
+      </c>
+      <c r="B98" t="s">
+        <v>719</v>
+      </c>
+      <c r="C98" t="s">
+        <v>720</v>
+      </c>
+      <c r="D98" t="s">
+        <v>261</v>
+      </c>
+      <c r="E98" t="s">
+        <v>721</v>
+      </c>
+      <c r="F98" t="s">
+        <v>291</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>723</v>
+      </c>
+      <c r="B99" t="s">
+        <v>724</v>
+      </c>
+      <c r="C99" t="s">
+        <v>130</v>
+      </c>
+      <c r="D99" t="s">
+        <v>261</v>
+      </c>
+      <c r="E99" t="s">
+        <v>536</v>
+      </c>
+      <c r="F99" t="s">
+        <v>725</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>727</v>
+      </c>
+      <c r="B100" t="s">
+        <v>728</v>
+      </c>
+      <c r="C100" t="s">
+        <v>243</v>
+      </c>
+      <c r="D100" t="s">
+        <v>261</v>
+      </c>
+      <c r="E100" t="s">
+        <v>562</v>
+      </c>
+      <c r="F100" t="s">
+        <v>729</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>731</v>
+      </c>
+      <c r="B101" t="s">
+        <v>732</v>
+      </c>
+      <c r="C101" t="s">
+        <v>733</v>
+      </c>
+      <c r="D101" t="s">
+        <v>261</v>
+      </c>
+      <c r="E101" t="s">
+        <v>542</v>
+      </c>
+      <c r="F101" t="s">
+        <v>269</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>735</v>
+      </c>
+      <c r="B102" t="s">
+        <v>736</v>
+      </c>
+      <c r="C102" t="s">
+        <v>737</v>
+      </c>
+      <c r="D102" t="s">
+        <v>261</v>
+      </c>
+      <c r="E102" t="s">
+        <v>738</v>
+      </c>
+      <c r="F102" t="s">
+        <v>739</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>741</v>
+      </c>
+      <c r="B103" t="s">
+        <v>742</v>
+      </c>
+      <c r="C103" t="s">
+        <v>743</v>
+      </c>
+      <c r="D103" t="s">
+        <v>261</v>
+      </c>
+      <c r="E103" t="s">
+        <v>644</v>
+      </c>
+      <c r="F103" t="s">
+        <v>744</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>746</v>
+      </c>
+      <c r="B104" t="s">
+        <v>724</v>
+      </c>
+      <c r="C104" t="s">
+        <v>130</v>
+      </c>
+      <c r="D104" t="s">
+        <v>261</v>
+      </c>
+      <c r="E104" t="s">
+        <v>747</v>
+      </c>
+      <c r="F104" t="s">
+        <v>725</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>749</v>
+      </c>
+      <c r="B105" t="s">
+        <v>750</v>
+      </c>
+      <c r="C105" t="s">
+        <v>751</v>
+      </c>
+      <c r="D105" t="s">
+        <v>261</v>
+      </c>
+      <c r="E105" t="s">
+        <v>752</v>
+      </c>
+      <c r="F105" t="s">
+        <v>753</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>749</v>
+      </c>
+      <c r="B106" t="s">
+        <v>750</v>
+      </c>
+      <c r="C106" t="s">
+        <v>755</v>
+      </c>
+      <c r="D106" t="s">
+        <v>261</v>
+      </c>
+      <c r="E106" t="s">
+        <v>752</v>
+      </c>
+      <c r="F106" t="s">
+        <v>753</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>757</v>
+      </c>
+      <c r="B107" t="s">
+        <v>134</v>
+      </c>
+      <c r="C107" t="s">
+        <v>758</v>
+      </c>
+      <c r="D107" t="s">
+        <v>261</v>
+      </c>
+      <c r="E107" t="s">
+        <v>759</v>
+      </c>
+      <c r="F107" t="s">
+        <v>760</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>762</v>
+      </c>
+      <c r="B108" t="s">
+        <v>535</v>
+      </c>
+      <c r="C108" t="s">
+        <v>720</v>
+      </c>
+      <c r="D108" t="s">
+        <v>261</v>
+      </c>
+      <c r="E108" t="s">
+        <v>763</v>
+      </c>
+      <c r="F108" t="s">
+        <v>291</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>765</v>
+      </c>
+      <c r="B109" t="s">
+        <v>766</v>
+      </c>
+      <c r="C109" t="s">
+        <v>767</v>
+      </c>
+      <c r="D109" t="s">
+        <v>261</v>
+      </c>
+      <c r="E109" t="s">
+        <v>768</v>
+      </c>
+      <c r="F109" t="s">
+        <v>769</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>771</v>
+      </c>
+      <c r="B110" t="s">
+        <v>772</v>
+      </c>
+      <c r="C110" t="s">
+        <v>773</v>
+      </c>
+      <c r="D110" t="s">
+        <v>261</v>
+      </c>
+      <c r="E110" t="s">
+        <v>774</v>
+      </c>
+      <c r="F110" t="s">
+        <v>775</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>777</v>
+      </c>
+      <c r="B111" t="s">
+        <v>778</v>
+      </c>
+      <c r="C111" t="s">
+        <v>416</v>
+      </c>
+      <c r="D111" t="s">
+        <v>261</v>
+      </c>
+      <c r="E111" t="s">
+        <v>567</v>
+      </c>
+      <c r="F111" t="s">
+        <v>779</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>780</v>
       </c>
     </row>
   </sheetData>
@@ -5779,6 +7207,45 @@
     <hyperlink ref="H70" r:id="rId69"/>
     <hyperlink ref="H71" r:id="rId70"/>
     <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5828,13 +7295,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>604</v>
+        <v>781</v>
       </c>
       <c r="B2" t="s">
-        <v>605</v>
+        <v>782</v>
       </c>
       <c r="C2" t="s">
-        <v>338</v>
+        <v>370</v>
       </c>
       <c r="D2" t="s">
         <v>291</v>
@@ -5843,21 +7310,21 @@
         <v>291</v>
       </c>
       <c r="F2" t="s">
-        <v>606</v>
+        <v>783</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>607</v>
+        <v>784</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>608</v>
+        <v>785</v>
       </c>
       <c r="B3" t="s">
-        <v>609</v>
+        <v>786</v>
       </c>
       <c r="C3" t="s">
-        <v>610</v>
+        <v>787</v>
       </c>
       <c r="D3" t="s">
         <v>291</v>
@@ -5866,21 +7333,21 @@
         <v>291</v>
       </c>
       <c r="F3" t="s">
-        <v>611</v>
+        <v>788</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>612</v>
+        <v>789</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>613</v>
+        <v>790</v>
       </c>
       <c r="B4" t="s">
-        <v>614</v>
+        <v>791</v>
       </c>
       <c r="C4" t="s">
-        <v>615</v>
+        <v>792</v>
       </c>
       <c r="D4" t="s">
         <v>291</v>
@@ -5889,21 +7356,21 @@
         <v>291</v>
       </c>
       <c r="F4" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>617</v>
+        <v>794</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>618</v>
+        <v>795</v>
       </c>
       <c r="B5" t="s">
-        <v>619</v>
+        <v>796</v>
       </c>
       <c r="C5" t="s">
-        <v>620</v>
+        <v>797</v>
       </c>
       <c r="D5" t="s">
         <v>291</v>
@@ -5912,21 +7379,21 @@
         <v>291</v>
       </c>
       <c r="F5" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>621</v>
+        <v>798</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>622</v>
+        <v>799</v>
       </c>
       <c r="B6" t="s">
-        <v>623</v>
+        <v>800</v>
       </c>
       <c r="C6" t="s">
-        <v>624</v>
+        <v>801</v>
       </c>
       <c r="D6" t="s">
         <v>291</v>
@@ -5935,21 +7402,21 @@
         <v>291</v>
       </c>
       <c r="F6" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>625</v>
+        <v>802</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>626</v>
+        <v>803</v>
       </c>
       <c r="B7" t="s">
-        <v>627</v>
+        <v>804</v>
       </c>
       <c r="C7" t="s">
-        <v>628</v>
+        <v>805</v>
       </c>
       <c r="D7" t="s">
         <v>291</v>
@@ -5958,21 +7425,21 @@
         <v>291</v>
       </c>
       <c r="F7" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>629</v>
+        <v>806</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>630</v>
+        <v>807</v>
       </c>
       <c r="B8" t="s">
-        <v>631</v>
+        <v>808</v>
       </c>
       <c r="C8" t="s">
-        <v>632</v>
+        <v>809</v>
       </c>
       <c r="D8" t="s">
         <v>291</v>
@@ -5981,21 +7448,21 @@
         <v>291</v>
       </c>
       <c r="F8" t="s">
-        <v>611</v>
+        <v>788</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>633</v>
+        <v>810</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>634</v>
+        <v>811</v>
       </c>
       <c r="B9" t="s">
-        <v>635</v>
+        <v>812</v>
       </c>
       <c r="C9" t="s">
-        <v>636</v>
+        <v>813</v>
       </c>
       <c r="D9" t="s">
         <v>291</v>
@@ -6004,21 +7471,21 @@
         <v>291</v>
       </c>
       <c r="F9" t="s">
-        <v>637</v>
+        <v>814</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>638</v>
+        <v>815</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>639</v>
+        <v>816</v>
       </c>
       <c r="B10" t="s">
-        <v>640</v>
+        <v>817</v>
       </c>
       <c r="C10" t="s">
-        <v>641</v>
+        <v>818</v>
       </c>
       <c r="D10" t="s">
         <v>291</v>
@@ -6027,21 +7494,21 @@
         <v>291</v>
       </c>
       <c r="F10" t="s">
-        <v>637</v>
+        <v>814</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>642</v>
+        <v>819</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>643</v>
+        <v>820</v>
       </c>
       <c r="B11" t="s">
-        <v>644</v>
+        <v>821</v>
       </c>
       <c r="C11" t="s">
-        <v>645</v>
+        <v>822</v>
       </c>
       <c r="D11" t="s">
         <v>291</v>
@@ -6050,21 +7517,21 @@
         <v>291</v>
       </c>
       <c r="F11" t="s">
-        <v>646</v>
+        <v>823</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>647</v>
+        <v>824</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>648</v>
+        <v>825</v>
       </c>
       <c r="B12" t="s">
-        <v>649</v>
+        <v>826</v>
       </c>
       <c r="C12" t="s">
-        <v>650</v>
+        <v>827</v>
       </c>
       <c r="D12" t="s">
         <v>291</v>
@@ -6073,21 +7540,21 @@
         <v>291</v>
       </c>
       <c r="F12" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>651</v>
+        <v>828</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>652</v>
+        <v>829</v>
       </c>
       <c r="B13" t="s">
-        <v>653</v>
+        <v>830</v>
       </c>
       <c r="C13" t="s">
-        <v>654</v>
+        <v>831</v>
       </c>
       <c r="D13" t="s">
         <v>291</v>
@@ -6096,21 +7563,21 @@
         <v>291</v>
       </c>
       <c r="F13" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>655</v>
+        <v>832</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>656</v>
+        <v>833</v>
       </c>
       <c r="B14" t="s">
-        <v>657</v>
+        <v>834</v>
       </c>
       <c r="C14" t="s">
-        <v>658</v>
+        <v>835</v>
       </c>
       <c r="D14" t="s">
         <v>291</v>
@@ -6119,21 +7586,21 @@
         <v>291</v>
       </c>
       <c r="F14" t="s">
-        <v>659</v>
+        <v>836</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>660</v>
+        <v>837</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>661</v>
+        <v>838</v>
       </c>
       <c r="B15" t="s">
-        <v>662</v>
+        <v>839</v>
       </c>
       <c r="C15" t="s">
-        <v>663</v>
+        <v>840</v>
       </c>
       <c r="D15" t="s">
         <v>291</v>
@@ -6142,21 +7609,21 @@
         <v>291</v>
       </c>
       <c r="F15" t="s">
-        <v>567</v>
+        <v>696</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>664</v>
+        <v>841</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>665</v>
+        <v>842</v>
       </c>
       <c r="B16" t="s">
-        <v>666</v>
+        <v>843</v>
       </c>
       <c r="C16" t="s">
-        <v>667</v>
+        <v>844</v>
       </c>
       <c r="D16" t="s">
         <v>291</v>
@@ -6165,21 +7632,21 @@
         <v>291</v>
       </c>
       <c r="F16" t="s">
-        <v>567</v>
+        <v>696</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>668</v>
+        <v>845</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>669</v>
+        <v>846</v>
       </c>
       <c r="B17" t="s">
-        <v>670</v>
+        <v>847</v>
       </c>
       <c r="C17" t="s">
-        <v>654</v>
+        <v>831</v>
       </c>
       <c r="D17" t="s">
         <v>291</v>
@@ -6191,18 +7658,18 @@
         <v>248</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>671</v>
+        <v>848</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>672</v>
+        <v>849</v>
       </c>
       <c r="B18" t="s">
-        <v>673</v>
+        <v>850</v>
       </c>
       <c r="C18" t="s">
-        <v>674</v>
+        <v>851</v>
       </c>
       <c r="D18" t="s">
         <v>291</v>
@@ -6211,21 +7678,21 @@
         <v>291</v>
       </c>
       <c r="F18" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>675</v>
+        <v>852</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>672</v>
+        <v>849</v>
       </c>
       <c r="B19" t="s">
-        <v>676</v>
+        <v>853</v>
       </c>
       <c r="C19" t="s">
-        <v>677</v>
+        <v>854</v>
       </c>
       <c r="D19" t="s">
         <v>291</v>
@@ -6234,21 +7701,21 @@
         <v>291</v>
       </c>
       <c r="F19" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>678</v>
+        <v>855</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>672</v>
+        <v>849</v>
       </c>
       <c r="B20" t="s">
-        <v>679</v>
+        <v>856</v>
       </c>
       <c r="C20" t="s">
-        <v>680</v>
+        <v>857</v>
       </c>
       <c r="D20" t="s">
         <v>291</v>
@@ -6257,21 +7724,21 @@
         <v>291</v>
       </c>
       <c r="F20" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>681</v>
+        <v>858</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>672</v>
+        <v>849</v>
       </c>
       <c r="B21" t="s">
-        <v>682</v>
+        <v>859</v>
       </c>
       <c r="C21" t="s">
-        <v>683</v>
+        <v>860</v>
       </c>
       <c r="D21" t="s">
         <v>291</v>
@@ -6280,21 +7747,21 @@
         <v>291</v>
       </c>
       <c r="F21" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>684</v>
+        <v>861</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>672</v>
+        <v>849</v>
       </c>
       <c r="B22" t="s">
-        <v>685</v>
+        <v>862</v>
       </c>
       <c r="C22" t="s">
-        <v>686</v>
+        <v>863</v>
       </c>
       <c r="D22" t="s">
         <v>291</v>
@@ -6303,21 +7770,21 @@
         <v>291</v>
       </c>
       <c r="F22" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>687</v>
+        <v>864</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>672</v>
+        <v>849</v>
       </c>
       <c r="B23" t="s">
-        <v>688</v>
+        <v>865</v>
       </c>
       <c r="C23" t="s">
-        <v>689</v>
+        <v>866</v>
       </c>
       <c r="D23" t="s">
         <v>291</v>
@@ -6326,21 +7793,21 @@
         <v>291</v>
       </c>
       <c r="F23" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>690</v>
+        <v>867</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>672</v>
+        <v>849</v>
       </c>
       <c r="B24" t="s">
-        <v>691</v>
+        <v>868</v>
       </c>
       <c r="C24" t="s">
-        <v>692</v>
+        <v>869</v>
       </c>
       <c r="D24" t="s">
         <v>291</v>
@@ -6349,21 +7816,21 @@
         <v>291</v>
       </c>
       <c r="F24" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>693</v>
+        <v>870</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>694</v>
+        <v>871</v>
       </c>
       <c r="B25" t="s">
-        <v>695</v>
+        <v>872</v>
       </c>
       <c r="C25" t="s">
-        <v>696</v>
+        <v>873</v>
       </c>
       <c r="D25" t="s">
         <v>291</v>
@@ -6372,21 +7839,21 @@
         <v>291</v>
       </c>
       <c r="F25" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>697</v>
+        <v>874</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>698</v>
+        <v>875</v>
       </c>
       <c r="B26" t="s">
-        <v>699</v>
+        <v>876</v>
       </c>
       <c r="C26" t="s">
-        <v>700</v>
+        <v>877</v>
       </c>
       <c r="D26" t="s">
         <v>291</v>
@@ -6395,21 +7862,21 @@
         <v>291</v>
       </c>
       <c r="F26" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>701</v>
+        <v>878</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>702</v>
+        <v>879</v>
       </c>
       <c r="B27" t="s">
-        <v>703</v>
+        <v>880</v>
       </c>
       <c r="C27" t="s">
-        <v>704</v>
+        <v>881</v>
       </c>
       <c r="D27" t="s">
         <v>291</v>
@@ -6418,21 +7885,21 @@
         <v>291</v>
       </c>
       <c r="F27" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>705</v>
+        <v>882</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>706</v>
+        <v>883</v>
       </c>
       <c r="B28" t="s">
-        <v>707</v>
+        <v>884</v>
       </c>
       <c r="C28" t="s">
-        <v>708</v>
+        <v>885</v>
       </c>
       <c r="D28" t="s">
         <v>291</v>
@@ -6441,21 +7908,21 @@
         <v>291</v>
       </c>
       <c r="F28" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>709</v>
+        <v>886</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>710</v>
+        <v>887</v>
       </c>
       <c r="B29" t="s">
-        <v>711</v>
+        <v>888</v>
       </c>
       <c r="C29" t="s">
-        <v>712</v>
+        <v>889</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -6464,21 +7931,21 @@
         <v>291</v>
       </c>
       <c r="F29" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>713</v>
+        <v>890</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>714</v>
+        <v>891</v>
       </c>
       <c r="B30" t="s">
-        <v>715</v>
+        <v>892</v>
       </c>
       <c r="C30" t="s">
-        <v>716</v>
+        <v>893</v>
       </c>
       <c r="D30" t="s">
         <v>291</v>
@@ -6487,21 +7954,21 @@
         <v>291</v>
       </c>
       <c r="F30" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>717</v>
+        <v>894</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>718</v>
+        <v>895</v>
       </c>
       <c r="B31" t="s">
-        <v>719</v>
+        <v>896</v>
       </c>
       <c r="C31" t="s">
-        <v>720</v>
+        <v>897</v>
       </c>
       <c r="D31" t="s">
         <v>291</v>
@@ -6510,21 +7977,21 @@
         <v>291</v>
       </c>
       <c r="F31" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>721</v>
+        <v>898</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>722</v>
+        <v>899</v>
       </c>
       <c r="B32" t="s">
-        <v>723</v>
+        <v>900</v>
       </c>
       <c r="C32" t="s">
-        <v>654</v>
+        <v>831</v>
       </c>
       <c r="D32" t="s">
         <v>291</v>
@@ -6533,21 +8000,21 @@
         <v>291</v>
       </c>
       <c r="F32" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>724</v>
+        <v>901</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>725</v>
+        <v>902</v>
       </c>
       <c r="B33" t="s">
-        <v>726</v>
+        <v>903</v>
       </c>
       <c r="C33" t="s">
-        <v>727</v>
+        <v>904</v>
       </c>
       <c r="D33" t="s">
         <v>291</v>
@@ -6556,21 +8023,21 @@
         <v>291</v>
       </c>
       <c r="F33" t="s">
-        <v>659</v>
+        <v>836</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>728</v>
+        <v>905</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>729</v>
+        <v>906</v>
       </c>
       <c r="B34" t="s">
-        <v>719</v>
+        <v>896</v>
       </c>
       <c r="C34" t="s">
-        <v>720</v>
+        <v>897</v>
       </c>
       <c r="D34" t="s">
         <v>291</v>
@@ -6579,21 +8046,21 @@
         <v>291</v>
       </c>
       <c r="F34" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>730</v>
+        <v>907</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>731</v>
+        <v>908</v>
       </c>
       <c r="B35" t="s">
-        <v>732</v>
+        <v>909</v>
       </c>
       <c r="C35" t="s">
-        <v>733</v>
+        <v>910</v>
       </c>
       <c r="D35" t="s">
         <v>291</v>
@@ -6602,21 +8069,21 @@
         <v>291</v>
       </c>
       <c r="F35" t="s">
-        <v>659</v>
+        <v>836</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>734</v>
+        <v>911</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>735</v>
+        <v>912</v>
       </c>
       <c r="B36" t="s">
-        <v>736</v>
+        <v>913</v>
       </c>
       <c r="C36" t="s">
-        <v>737</v>
+        <v>914</v>
       </c>
       <c r="D36" t="s">
         <v>291</v>
@@ -6625,21 +8092,21 @@
         <v>291</v>
       </c>
       <c r="F36" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>738</v>
+        <v>915</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>739</v>
+        <v>916</v>
       </c>
       <c r="B37" t="s">
-        <v>740</v>
+        <v>917</v>
       </c>
       <c r="C37" t="s">
-        <v>741</v>
+        <v>918</v>
       </c>
       <c r="D37" t="s">
         <v>291</v>
@@ -6648,21 +8115,21 @@
         <v>291</v>
       </c>
       <c r="F37" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>742</v>
+        <v>919</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>743</v>
+        <v>920</v>
       </c>
       <c r="B38" t="s">
-        <v>744</v>
+        <v>921</v>
       </c>
       <c r="C38" t="s">
-        <v>745</v>
+        <v>922</v>
       </c>
       <c r="D38" t="s">
         <v>291</v>
@@ -6671,21 +8138,21 @@
         <v>291</v>
       </c>
       <c r="F38" t="s">
-        <v>746</v>
+        <v>923</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>747</v>
+        <v>924</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>748</v>
+        <v>925</v>
       </c>
       <c r="B39" t="s">
-        <v>749</v>
+        <v>926</v>
       </c>
       <c r="C39" t="s">
-        <v>750</v>
+        <v>927</v>
       </c>
       <c r="D39" t="s">
         <v>291</v>
@@ -6694,21 +8161,21 @@
         <v>291</v>
       </c>
       <c r="F39" t="s">
-        <v>611</v>
+        <v>788</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>751</v>
+        <v>928</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>752</v>
+        <v>929</v>
       </c>
       <c r="B40" t="s">
-        <v>753</v>
+        <v>930</v>
       </c>
       <c r="C40" t="s">
-        <v>632</v>
+        <v>809</v>
       </c>
       <c r="D40" t="s">
         <v>291</v>
@@ -6717,21 +8184,21 @@
         <v>291</v>
       </c>
       <c r="F40" t="s">
-        <v>637</v>
+        <v>814</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>754</v>
+        <v>931</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>755</v>
+        <v>932</v>
       </c>
       <c r="B41" t="s">
-        <v>756</v>
+        <v>933</v>
       </c>
       <c r="C41" t="s">
-        <v>757</v>
+        <v>934</v>
       </c>
       <c r="D41" t="s">
         <v>291</v>
@@ -6740,21 +8207,21 @@
         <v>291</v>
       </c>
       <c r="F41" t="s">
-        <v>758</v>
+        <v>935</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>759</v>
+        <v>936</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>760</v>
+        <v>937</v>
       </c>
       <c r="B42" t="s">
-        <v>761</v>
+        <v>938</v>
       </c>
       <c r="C42" t="s">
-        <v>762</v>
+        <v>939</v>
       </c>
       <c r="D42" t="s">
         <v>291</v>
@@ -6763,21 +8230,21 @@
         <v>291</v>
       </c>
       <c r="F42" t="s">
-        <v>746</v>
+        <v>923</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>763</v>
+        <v>940</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>764</v>
+        <v>941</v>
       </c>
       <c r="B43" t="s">
-        <v>765</v>
+        <v>942</v>
       </c>
       <c r="C43" t="s">
-        <v>766</v>
+        <v>943</v>
       </c>
       <c r="D43" t="s">
         <v>291</v>
@@ -6786,21 +8253,21 @@
         <v>291</v>
       </c>
       <c r="F43" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>767</v>
+        <v>944</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>768</v>
+        <v>945</v>
       </c>
       <c r="B44" t="s">
-        <v>769</v>
+        <v>946</v>
       </c>
       <c r="C44" t="s">
-        <v>770</v>
+        <v>947</v>
       </c>
       <c r="D44" t="s">
         <v>291</v>
@@ -6809,21 +8276,21 @@
         <v>291</v>
       </c>
       <c r="F44" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>771</v>
+        <v>948</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>772</v>
+        <v>949</v>
       </c>
       <c r="B45" t="s">
-        <v>773</v>
+        <v>950</v>
       </c>
       <c r="C45" t="s">
-        <v>654</v>
+        <v>831</v>
       </c>
       <c r="D45" t="s">
         <v>291</v>
@@ -6832,21 +8299,21 @@
         <v>291</v>
       </c>
       <c r="F45" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>774</v>
+        <v>951</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>775</v>
+        <v>952</v>
       </c>
       <c r="B46" t="s">
-        <v>776</v>
+        <v>953</v>
       </c>
       <c r="C46" t="s">
-        <v>777</v>
+        <v>954</v>
       </c>
       <c r="D46" t="s">
         <v>291</v>
@@ -6855,21 +8322,21 @@
         <v>291</v>
       </c>
       <c r="F46" t="s">
-        <v>758</v>
+        <v>935</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>778</v>
+        <v>955</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>779</v>
+        <v>956</v>
       </c>
       <c r="B47" t="s">
-        <v>780</v>
+        <v>957</v>
       </c>
       <c r="C47" t="s">
-        <v>781</v>
+        <v>958</v>
       </c>
       <c r="D47" t="s">
         <v>291</v>
@@ -6878,21 +8345,21 @@
         <v>291</v>
       </c>
       <c r="F47" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>782</v>
+        <v>959</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>783</v>
+        <v>960</v>
       </c>
       <c r="B48" t="s">
-        <v>784</v>
+        <v>961</v>
       </c>
       <c r="C48" t="s">
-        <v>785</v>
+        <v>962</v>
       </c>
       <c r="D48" t="s">
         <v>291</v>
@@ -6901,21 +8368,21 @@
         <v>291</v>
       </c>
       <c r="F48" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>786</v>
+        <v>963</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>787</v>
+        <v>964</v>
       </c>
       <c r="B49" t="s">
-        <v>788</v>
+        <v>965</v>
       </c>
       <c r="C49" t="s">
-        <v>632</v>
+        <v>809</v>
       </c>
       <c r="D49" t="s">
         <v>291</v>
@@ -6924,21 +8391,21 @@
         <v>291</v>
       </c>
       <c r="F49" t="s">
-        <v>758</v>
+        <v>935</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>789</v>
+        <v>966</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>790</v>
+        <v>967</v>
       </c>
       <c r="B50" t="s">
-        <v>791</v>
+        <v>968</v>
       </c>
       <c r="C50" t="s">
-        <v>792</v>
+        <v>969</v>
       </c>
       <c r="D50" t="s">
         <v>291</v>
@@ -6947,10 +8414,10 @@
         <v>291</v>
       </c>
       <c r="F50" t="s">
-        <v>616</v>
+        <v>793</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>793</v>
+        <v>970</v>
       </c>
     </row>
   </sheetData>
